--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A473565F-95A7-4153-9432-4F3420E5DC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -347,20 +347,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5832,51 +5832,51 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="N2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="N2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="V2" s="5" t="s">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="V2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
     </row>
     <row r="72" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N72" s="6" t="s">
+      <c r="N72" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
     </row>
     <row r="74" spans="14:18" x14ac:dyDescent="0.35">
       <c r="N74" t="s">
@@ -5904,13 +5904,13 @@
       </c>
     </row>
     <row r="80" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N80" s="6" t="s">
+      <c r="N80" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
     </row>
     <row r="82" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N82" t="s">
@@ -5995,14 +5995,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -6111,7 +6111,7 @@
       <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F9" t="s">
@@ -6213,7 +6213,7 @@
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E19" s="7"/>
+      <c r="E19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6229,20 +6229,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A473565F-95A7-4153-9432-4F3420E5DC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEFB19-FE45-4809-969E-1BA9D99C0650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
     <sheet name="Parameter Details" sheetId="3" r:id="rId2"/>
     <sheet name="Movement dataset" sheetId="2" r:id="rId3"/>
+    <sheet name="suppl" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
   <si>
     <t>ALPHA_PREFIX_WEIGHT     = 0.65</t>
   </si>
@@ -260,6 +261,99 @@
   </si>
   <si>
     <t>Less information per tree</t>
+  </si>
+  <si>
+    <t>Allowing up to 100 attempts greatly increases the chance of obtaining a valid split without running indefinitely.</t>
+  </si>
+  <si>
+    <t>why it's not 0.15? Because validation is taken after removing the test set.</t>
+  </si>
+  <si>
+    <t>15% of data reserved for final testing.</t>
+  </si>
+  <si>
+    <t>allows each tree to use 80% of the available features.</t>
+  </si>
+  <si>
+    <t>Current Workflow Application [06/08/2026]</t>
+  </si>
+  <si>
+    <t>PARAMETER SGD Classifier</t>
+  </si>
+  <si>
+    <t>&lt;0.65</t>
+  </si>
+  <si>
+    <t>&lt;0.90</t>
+  </si>
+  <si>
+    <t>&lt;0.60</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
+  </si>
+  <si>
+    <t>&gt;0.65</t>
+  </si>
+  <si>
+    <t>&gt;0.90</t>
+  </si>
+  <si>
+    <t>&gt;0.60</t>
+  </si>
+  <si>
+    <t>&gt;5</t>
+  </si>
+  <si>
+    <t>Balances prefix matching and TF-IDF similarity</t>
+  </si>
+  <si>
+    <t>Relies more on TF-IDF; prefix becomes less influential</t>
+  </si>
+  <si>
+    <t>Relies more on prefix; may ignore useful text differences</t>
+  </si>
+  <si>
+    <t>Confidence assigned to dictionary-based predictions</t>
+  </si>
+  <si>
+    <t>Dictionary predictions become less trusted</t>
+  </si>
+  <si>
+    <t>Dictionary predictions become overly dominant</t>
+  </si>
+  <si>
+    <t>Minimum similarity required to accept TF-IDF prediction</t>
+  </si>
+  <si>
+    <t>More predictions accepted; higher false positives</t>
+  </si>
+  <si>
+    <t>Fewer predictions accepted; more UNKNOWN results</t>
+  </si>
+  <si>
+    <t>Minimum SGD confidence required to trust SGD prediction</t>
+  </si>
+  <si>
+    <t>&lt;0.70</t>
+  </si>
+  <si>
+    <t>&gt;0.70</t>
+  </si>
+  <si>
+    <t>Number of nearest neighbours considered during similarity search</t>
+  </si>
+  <si>
+    <t>Faster but may miss good candidates</t>
+  </si>
+  <si>
+    <t>More candidates considered but slower and potentially noisier</t>
+  </si>
+  <si>
+    <t>More SGD predictions accepted; higher error risk</t>
+  </si>
+  <si>
+    <t>Only very confident predictions accepted; more fallbacks</t>
   </si>
 </sst>
 </file>
@@ -343,12 +437,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -359,8 +456,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4053,6 +4159,2904 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>350874</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28258</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1732998" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053048D9-FE5A-4102-A72A-5DA9F2F93AE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17959912" y="760950"/>
+          <a:ext cx="1732998" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Source Dataset : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>DB SQL</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>101453</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>79042</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1059934" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{703FDC7F-C615-4767-9A70-27CBBF47AF51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18321068" y="1361254"/>
+          <a:ext cx="1059934" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Input</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> JSON</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>408421</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>26656</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1732998" cy="437873"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7440F9BF-89B3-4FB7-BF2E-5E0D6624EC5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18017459" y="2041560"/>
+          <a:ext cx="1732998" cy="437873"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Device</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t> Type Prediction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = SGD Classifier</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>330633</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>25862</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1732998" cy="437873"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E67417CD-6761-4206-A447-A429659F737E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17939671" y="3506150"/>
+          <a:ext cx="1732998" cy="437873"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Section </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>Prediction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = XGBoost</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>100107</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>18196</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2247541" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1D28F6-3E54-4D76-BB37-95566F56EFBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17709145" y="4231177"/>
+          <a:ext cx="2247541" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Output</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = Section Prediction</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>235342</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133686</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2071535" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D17522-3EAF-4369-B79B-692AC03FA7C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17844380" y="2881282"/>
+          <a:ext cx="2071535" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Output</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = Device Type Prediction</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>24976</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>24976</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>75867</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17343C1B-A944-44E4-9EC0-B420EBBFC051}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18855168" y="1030089"/>
+          <a:ext cx="0" cy="327990"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>25373</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>161833</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>25373</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>20306</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EF53A86-F7F4-4B19-B9CD-ECE855001D8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18855565" y="1627218"/>
+          <a:ext cx="0" cy="407992"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>6761</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>107341</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>6761</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>140036</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Straight Arrow Connector 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{504E1941-06EF-46C0-9FB7-AF74991E0A48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="2"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18836953" y="2488591"/>
+          <a:ext cx="0" cy="399041"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>4735</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>37883</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>4735</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19512</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552185D7-9883-4C8A-AD32-88509CDA745C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18834927" y="3151825"/>
+          <a:ext cx="0" cy="347975"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>4735</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>103372</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>4735</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>21371</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Arrow Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7064886-E837-4C16-8CC4-C1AB444A903C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="10" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18834927" y="3950007"/>
+          <a:ext cx="0" cy="284345"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>347303</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1732998" cy="437873"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="TextBox 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD7B8EA4-5E3B-4906-94B5-FA62524547E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17956341" y="4772580"/>
+          <a:ext cx="1732998" cy="437873"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Section </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>Prediction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = XGBoost</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>82583</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>20433</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2247541" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="TextBox 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B2B07A3-95A2-40C9-B913-C6CC0F12FD82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17691621" y="5515625"/>
+          <a:ext cx="2247541" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Output</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = Cluster Prediction</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>5530</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>107337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>5530</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>10780</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Arrow Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837ACBE4-0B47-46F9-B93E-5E098929F978}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="2"/>
+          <a:endCxn id="28" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18835722" y="4503491"/>
+          <a:ext cx="0" cy="269789"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>23664</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>97816</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>23664</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>26783</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Arrow Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21A39095-5ED9-49D9-ACD5-3DD6C013A85C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="28" idx="2"/>
+          <a:endCxn id="29" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="18853856" y="5226662"/>
+          <a:ext cx="0" cy="295313"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>602231</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>106000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>15575</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>88834</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Straight Arrow Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F95938D-72F4-4584-ADFB-AB4C15451554}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="29" idx="2"/>
+          <a:endCxn id="36" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18725301" y="5654792"/>
+          <a:ext cx="20643" cy="340821"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>468149</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>88834</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2738644" cy="991518"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="TextBox 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D34A4554-806B-4E8D-B0B4-0A6F122F7467}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17376622" y="5995613"/>
+          <a:ext cx="2738644" cy="991518"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Quota constraint cluster allocation (Logic)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>-  assign by prediction socre</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>- check cluster score</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>- resolve exceeded/vacant cluster</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>- create floating devices</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>227148</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>166469</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3522340" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="TextBox 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A8F4F18-C6CF-4495-BF31-5F2989416B90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17214290" y="12902143"/>
+          <a:ext cx="3522340" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>list of unknown [PENDING - no</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> output in console apps]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="1" u="none">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>344359</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10568</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5E555AA-BB00-4922-829D-22E57D299727}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16180707" y="7481481"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>Assigned Devices </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>68855</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>159845</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65BCA9D0-56BA-46A4-9E3A-F464272C48E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20151566" y="7378792"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>floating cluster</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>396115</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>34766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>464974</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>7393</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Connector: Elbow 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABCEE10A-FDF6-4BE1-0C32-9BFDEAE8D1BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="1"/>
+          <a:endCxn id="45" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="16845376" y="6594592"/>
+          <a:ext cx="681772" cy="883714"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>287504</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>92076</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>154065</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>159845</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="57" name="Connector: Elbow 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9213EB30-146B-59BA-6C98-F28F3F91C82B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="46" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20370215" y="6228181"/>
+          <a:ext cx="478166" cy="1150611"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>349960</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>141469</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="TextBox 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D1BBD85-C778-4120-8F12-45222F83B2E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16151434" y="8082311"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Logic.dll</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>426765</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>102481</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1668735" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="TextBox 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAD6E39-9CB6-45E2-948A-653B5FBCE78C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17366611" y="9261135"/>
+          <a:ext cx="1668735" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Split KNOWN/UNKNOWN</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>406199</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>48257</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>41097</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>105656</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="82" name="Straight Arrow Connector 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8ADCA3E-15FA-48A7-A415-37324F0F4706}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="72" idx="2"/>
+          <a:endCxn id="73" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16819278" y="8350046"/>
+          <a:ext cx="1469714" cy="779294"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>163166</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>54763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>429941</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>154042</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="87" name="Connector: Elbow 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A2D3D8-B141-44C5-90DA-1ECA13EA614A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="73" idx="1"/>
+          <a:endCxn id="90" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="17103012" y="9396590"/>
+          <a:ext cx="266775" cy="648798"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>109805</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>154042</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="90" name="TextBox 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CC1749E-DCAE-46AB-918E-9E138ECF1AAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16441517" y="10045388"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>KNOWN</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>213190</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>126512</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="93" name="TextBox 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F08896DE-8198-41DF-9135-C5B517C44ED5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18977440" y="10017858"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>UNKNOWN</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>274271</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>54763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>272899</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123337</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="94" name="Connector: Elbow 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B6784CE-A7F7-4774-9DF9-1E1F8D04034E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="73" idx="3"/>
+          <a:endCxn id="93" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19038521" y="9396590"/>
+          <a:ext cx="606763" cy="618093"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>102118</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123838</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="98" name="TextBox 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF296504-8A1F-4801-B93C-F03589DBFDF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16433830" y="10747876"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Build</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> Cluster Group</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>102119</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>126678</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="TextBox 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCDB7F1-F635-4637-9120-977D260D80FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16433831" y="11300236"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Print</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> Cluster Table</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>159695</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>88110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>159695</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>142888</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="100" name="Straight Arrow Connector 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84480F4E-5D07-47F5-ACF1-9483F4E1F9B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="90" idx="2"/>
+          <a:endCxn id="98" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17099541" y="10345802"/>
+          <a:ext cx="0" cy="421124"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>148834</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>174294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>148834</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>126678</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="104" name="Straight Arrow Connector 103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8216A3D-F65A-4CE9-A161-48568FEAF12C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="98" idx="2"/>
+          <a:endCxn id="99" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="17088680" y="10981506"/>
+          <a:ext cx="0" cy="318730"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>240928</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>67233</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="114" name="TextBox 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D11D403-A6F6-4E09-A423-BF14D7C4A436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19005178" y="10691271"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Build</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> Cluster Group</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>240928</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>67233</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="115" name="TextBox 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D4D37B-5B60-4FB9-BC7D-8F46B08C719E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19005178" y="10691271"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Dump JSON</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>231904</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>126387</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="116" name="TextBox 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBB65AA4-2437-4F0B-B4C6-C1A5489C92FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18996154" y="11299945"/>
+          <a:ext cx="1329337" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>Manual correction</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>271006</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>24021</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>292394</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>64058</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="117" name="Straight Arrow Connector 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2F93E5-A87D-487E-A238-90038BD4B003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="93" idx="2"/>
+          <a:endCxn id="115" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19698260" y="10212560"/>
+          <a:ext cx="21388" cy="403914"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>278616</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>141793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>278616</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>126387</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="120" name="Straight Arrow Connector 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC1BA5B-92E6-4618-9BC3-490616DA45ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="115" idx="2"/>
+          <a:endCxn id="116" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="19651001" y="10949005"/>
+          <a:ext cx="0" cy="350940"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>397423</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>91479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>406199</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>144644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="132" name="Straight Arrow Connector 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{260378DE-440A-4BD2-AD45-A3BDA77E54B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="45" idx="2"/>
+          <a:endCxn id="72" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16810502" y="7671374"/>
+          <a:ext cx="8776" cy="414112"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>548913</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>84571</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1663960" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="146" name="TextBox 145">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93066E93-A1B2-47F8-A7B6-565C1562B0BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20020018" y="8025413"/>
+          <a:ext cx="1663960" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>floating_deviceid.json</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>118744</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66632</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>154507</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>87746</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="147" name="Straight Arrow Connector 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5665CFC8-435B-4B29-B9CE-BC0EF0B790F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="46" idx="2"/>
+          <a:endCxn id="146" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20813060" y="7646527"/>
+          <a:ext cx="35763" cy="382061"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>227588</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>12250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="781240"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="163" name="TextBox 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9969C2D9-5416-4223-9263-1A333080ACB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19044814" y="11838233"/>
+          <a:ext cx="1329337" cy="781240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>Place into Cluster Group Update JSON Print Updated Section</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>284122</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>21426</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>291613</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>9075</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="170" name="Straight Arrow Connector 169">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A52250-A5B3-4768-BE26-BBA2AA8BC7ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="116" idx="2"/>
+          <a:endCxn id="163" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="19656507" y="11561330"/>
+          <a:ext cx="7491" cy="353995"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5500,6 +8504,110 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4097" name="AutoShape 1" descr="Generated image: Refined Device Identifier Workflow Pipeline">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A836F9-EDD7-5B86-A1D8-664937DDAA8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76915</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73177D3A-EA92-A9DF-60F4-A3035301DE98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="6088"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3282950" y="428625"/>
+          <a:ext cx="8376365" cy="12439650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5822,159 +8930,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="B2:AC92"/>
+  <dimension ref="B2:AI70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
     <col min="20" max="20" width="2.6328125" style="2" customWidth="1"/>
-    <col min="27" max="28" width="8.7265625" customWidth="1"/>
-    <col min="29" max="29" width="2.6328125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="8.7265625" customWidth="1"/>
+    <col min="28" max="28" width="2.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="N2" s="6" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="N2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="V2" s="6" t="s">
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="V2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AD2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:35" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
     </row>
-    <row r="72" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N72" s="4" t="s">
+    <row r="50" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
     </row>
-    <row r="74" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N74" t="s">
+    <row r="52" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N52" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N75" t="s">
+    <row r="53" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N53" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N76" t="s">
+    <row r="54" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N54" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N77" t="s">
+    <row r="55" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N55" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N78" t="s">
+    <row r="56" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N56" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N80" s="4" t="s">
+    <row r="58" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N58" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
     </row>
-    <row r="82" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N82" t="s">
+    <row r="60" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N60" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N83" t="s">
+    <row r="61" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N61" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N84" t="s">
+    <row r="62" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N85" t="s">
+    <row r="63" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N63" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N86" t="s">
+    <row r="64" spans="14:18" x14ac:dyDescent="0.35">
+      <c r="N64" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N87" t="s">
+    <row r="65" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N65" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N88" t="s">
+    <row r="66" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N66" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N89" t="s">
+    <row r="67" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N67" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N90" t="s">
+    <row r="68" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N68" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N91" t="s">
+    <row r="69" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N69" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="14:14" x14ac:dyDescent="0.35">
-      <c r="N92" t="s">
+    <row r="70" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N70" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="N80:R80"/>
+  <mergeCells count="7">
+    <mergeCell ref="AD2:AI2"/>
+    <mergeCell ref="N58:R58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="N72:R72"/>
+    <mergeCell ref="N50:R50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5983,240 +9100,363 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0681933B-6749-4A17-925F-E9EB49A25785}">
-  <dimension ref="B2:G19"/>
+  <dimension ref="B2:G29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.7265625" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" customWidth="1"/>
+    <col min="3" max="3" width="60.36328125" customWidth="1"/>
     <col min="4" max="4" width="13.6328125" customWidth="1"/>
-    <col min="5" max="5" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.81640625" customWidth="1"/>
     <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.1796875" customWidth="1"/>
+    <col min="7" max="7" width="61" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
+        <v>88</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
+        <v>89</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
+        <v>91</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
+        <v>92</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
+        <v>94</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
+        <v>95</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
+        <v>97</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
+        <v>103</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
+        <v>100</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
+        <v>101</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G24" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E19" s="3"/>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E29" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="B12:G12"/>
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6229,20 +9469,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6252,4 +9492,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF64B0D-5B81-4205-8202-EA1D03B0667B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEFB19-FE45-4809-969E-1BA9D99C0650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6B2230-7895-4260-ACE2-78B3CBF42BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
@@ -437,24 +437,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -468,6 +456,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2023,9 +2024,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>28139</xdr:colOff>
+      <xdr:colOff>23987</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>7295</xdr:rowOff>
+      <xdr:rowOff>3143</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2071535" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -2041,7 +2042,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8105339" y="2178995"/>
+          <a:off x="8083602" y="2201220"/>
           <a:ext cx="2071535" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2174,9 +2175,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>399256</xdr:colOff>
+      <xdr:colOff>396935</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>20201</xdr:rowOff>
+      <xdr:rowOff>25727</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="436786"/>
     <xdr:sp macro="" textlink="">
@@ -2192,7 +2193,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8476456" y="2734826"/>
+          <a:off x="8445560" y="2704633"/>
           <a:ext cx="1337221" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2272,15 +2273,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>450597</xdr:colOff>
+      <xdr:colOff>450474</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>173822</xdr:rowOff>
+      <xdr:rowOff>164664</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>459070</xdr:colOff>
+      <xdr:colOff>454795</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>10470</xdr:rowOff>
+      <xdr:rowOff>3143</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2298,8 +2299,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9137397" y="1802597"/>
-          <a:ext cx="8473" cy="379573"/>
+          <a:off x="9118224" y="1813222"/>
+          <a:ext cx="4321" cy="387998"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2331,15 +2332,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>459070</xdr:colOff>
+      <xdr:colOff>455711</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>96436</xdr:rowOff>
+      <xdr:rowOff>89109</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>463824</xdr:colOff>
+      <xdr:colOff>458327</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>20201</xdr:rowOff>
+      <xdr:rowOff>28902</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2357,8 +2358,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9145870" y="2449111"/>
-          <a:ext cx="4754" cy="285715"/>
+          <a:off x="9111555" y="2410828"/>
+          <a:ext cx="2616" cy="296980"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2390,9 +2391,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>421109</xdr:colOff>
+      <xdr:colOff>416072</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121946</xdr:rowOff>
+      <xdr:rowOff>107293</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="436786"/>
     <xdr:sp macro="" textlink="">
@@ -2408,7 +2409,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8498309" y="4103396"/>
+          <a:off x="8464697" y="4036356"/>
           <a:ext cx="1337221" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2487,15 +2488,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>476948</xdr:colOff>
+      <xdr:colOff>470171</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>102734</xdr:rowOff>
+      <xdr:rowOff>98054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>476948</xdr:colOff>
+      <xdr:colOff>477464</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>125121</xdr:rowOff>
+      <xdr:rowOff>104118</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2513,8 +2514,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9163748" y="3722234"/>
-          <a:ext cx="0" cy="384337"/>
+          <a:off x="9126015" y="3669929"/>
+          <a:ext cx="7293" cy="363252"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2546,9 +2547,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>569478</xdr:colOff>
+      <xdr:colOff>564013</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>20392</xdr:rowOff>
+      <xdr:rowOff>8913</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2247541" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -2564,7 +2565,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8037078" y="3458917"/>
+          <a:off x="8005419" y="3402194"/>
           <a:ext cx="2247541" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2620,15 +2621,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>463824</xdr:colOff>
+      <xdr:colOff>458327</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>106149</xdr:rowOff>
+      <xdr:rowOff>108500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>475637</xdr:colOff>
+      <xdr:colOff>470171</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>20392</xdr:rowOff>
+      <xdr:rowOff>12088</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2646,8 +2647,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9150624" y="3182724"/>
-          <a:ext cx="11813" cy="276193"/>
+          <a:off x="9114171" y="3144594"/>
+          <a:ext cx="11844" cy="260775"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2679,9 +2680,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>592039</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>9930</xdr:rowOff>
+      <xdr:colOff>581476</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>122612</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2247541" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -2697,7 +2698,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8059639" y="4896255"/>
+          <a:off x="8022882" y="4766050"/>
           <a:ext cx="2247541" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2753,15 +2754,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>474940</xdr:colOff>
+      <xdr:colOff>477464</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>20486</xdr:rowOff>
+      <xdr:rowOff>5123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>495774</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>6755</xdr:rowOff>
+      <xdr:colOff>487634</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>125787</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2779,8 +2780,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9161740" y="4544861"/>
-          <a:ext cx="20834" cy="348219"/>
+          <a:off x="9133308" y="4469967"/>
+          <a:ext cx="10170" cy="299258"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5628,15 +5629,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>287504</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>92076</xdr:rowOff>
+      <xdr:colOff>155618</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>38493</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
-      <xdr:colOff>154065</xdr:colOff>
+      <xdr:colOff>120749</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>159845</xdr:rowOff>
+      <xdr:rowOff>163020</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5648,13 +5649,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="36" idx="3"/>
           <a:endCxn id="46" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20370215" y="6228181"/>
-          <a:ext cx="478166" cy="1150611"/>
+          <a:off x="20177168" y="6553593"/>
+          <a:ext cx="574731" cy="848427"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6800,9 +6802,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>548913</xdr:colOff>
+      <xdr:colOff>512120</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>84571</xdr:rowOff>
+      <xdr:rowOff>65334</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1663960" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6818,7 +6820,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20020018" y="8025413"/>
+          <a:off x="19786238" y="7954275"/>
           <a:ext cx="1663960" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6870,15 +6872,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>36</xdr:col>
-      <xdr:colOff>118744</xdr:colOff>
+      <xdr:colOff>125231</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>66632</xdr:rowOff>
+      <xdr:rowOff>68992</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
-      <xdr:colOff>154507</xdr:colOff>
+      <xdr:colOff>133865</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>87746</xdr:rowOff>
+      <xdr:rowOff>68509</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6897,8 +6899,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20813060" y="7646527"/>
-          <a:ext cx="35763" cy="382061"/>
+          <a:off x="20609584" y="7599345"/>
+          <a:ext cx="8634" cy="358105"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8930,7 +8932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="B2:AI70"/>
+  <dimension ref="B2:AL70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
@@ -8939,60 +8941,63 @@
     <col min="28" max="28" width="2.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="2:38" x14ac:dyDescent="0.35">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="N2" s="7" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="N2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="V2" s="7" t="s">
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="V2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AD2" s="7" t="s">
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AD2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
+      <c r="AE2" s="8"/>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
+      <c r="AI2" s="8"/>
+      <c r="AJ2" s="8"/>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="12"/>
     </row>
-    <row r="15" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:38" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
     </row>
     <row r="50" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N50" s="5" t="s">
+      <c r="N50" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
     </row>
     <row r="52" spans="14:18" x14ac:dyDescent="0.35">
       <c r="N52" t="s">
@@ -9020,13 +9025,13 @@
       </c>
     </row>
     <row r="58" spans="14:18" x14ac:dyDescent="0.35">
-      <c r="N58" s="5" t="s">
+      <c r="N58" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
     </row>
     <row r="60" spans="14:18" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -9085,13 +9090,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AD2:AI2"/>
     <mergeCell ref="N58:R58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="V2:Z2"/>
     <mergeCell ref="N50:R50"/>
+    <mergeCell ref="AD2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9112,14 +9117,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -9128,13 +9133,13 @@
       <c r="C4" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="6" t="s">
         <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="6" t="s">
         <v>84</v>
       </c>
       <c r="G4" t="s">
@@ -9148,13 +9153,13 @@
       <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>85</v>
       </c>
       <c r="G5" t="s">
@@ -9168,13 +9173,13 @@
       <c r="C6" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="6" t="s">
         <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>86</v>
       </c>
       <c r="G6" t="s">
@@ -9188,13 +9193,13 @@
       <c r="C7" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G7" t="s">
@@ -9208,13 +9213,13 @@
       <c r="C8" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G8" t="s">
@@ -9222,14 +9227,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -9258,7 +9263,7 @@
       <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E15" t="s">
@@ -9278,7 +9283,7 @@
       <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E16" t="s">
@@ -9298,7 +9303,7 @@
       <c r="C17" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E17" t="s">
@@ -9318,7 +9323,7 @@
       <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E18" t="s">
@@ -9338,7 +9343,7 @@
       <c r="C19" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -9358,7 +9363,7 @@
       <c r="C20" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E20" t="s">
@@ -9378,7 +9383,7 @@
       <c r="C21" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E21" t="s">
@@ -9398,7 +9403,7 @@
       <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E22" t="s">
@@ -9412,42 +9417,42 @@
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -9469,20 +9474,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6B2230-7895-4260-ACE2-78B3CBF42BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A732D-812E-4F4C-BD19-9B58B7EDD54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
-    <sheet name="Parameter Details" sheetId="3" r:id="rId2"/>
-    <sheet name="Movement dataset" sheetId="2" r:id="rId3"/>
-    <sheet name="suppl" sheetId="4" r:id="rId4"/>
+    <sheet name="question" sheetId="5" r:id="rId2"/>
+    <sheet name="Parameter Details" sheetId="3" r:id="rId3"/>
+    <sheet name="Movement dataset" sheetId="2" r:id="rId4"/>
+    <sheet name="suppl" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
   <si>
     <t>ALPHA_PREFIX_WEIGHT     = 0.65</t>
   </si>
@@ -354,13 +355,200 @@
   </si>
   <si>
     <t>Only very confident predictions accepted; more fallbacks</t>
+  </si>
+  <si>
+    <t>Model/Services/PythonSQL.cs</t>
+  </si>
+  <si>
+    <t>Filepath script</t>
+  </si>
+  <si>
+    <t>CURRENT DLL LIBRARY</t>
+  </si>
+  <si>
+    <t>Model.dll</t>
+  </si>
+  <si>
+    <t>Logic.dll</t>
+  </si>
+  <si>
+    <t>** both is work as reference for the consoleapp</t>
+  </si>
+  <si>
+    <t>** hence only carry on both dll library to handover for UI</t>
+  </si>
+  <si>
+    <t>STOP HERE</t>
+  </si>
+  <si>
+    <t>TROUBLESHOOTING THE FLOATING DUMP AND UNKNOWN DUMP</t>
+  </si>
+  <si>
+    <t>unknown_dump.json</t>
+  </si>
+  <si>
+    <t>Single shared file</t>
+  </si>
+  <si>
+    <r>
+      <t>🔴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Critical — will break outside your machine</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. The CSV export path is still hardcoded to your user folder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Program.cs:217):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. The SQL table name is hardcoded to one specific customer's table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Program.cs:165, 170):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🟠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> High — business rules baked into source, not data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The entire quotas list is hardcoded C# object-initializer code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Program.cs:252-291) — ~40 lines defining cluster capacity per Section/Cluster/DeviceType, specific to one customer's plant layout ("SECTION 2", CLUSTER 1-8).</t>
+    </r>
+  </si>
+  <si>
+    <t>COMMENTS: need to find the the algorithm. Make it in dll library</t>
+  </si>
+  <si>
+    <r>
+      <t>🟡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Medium — architectural gap for the DLL handover itself</t>
+    </r>
+  </si>
+  <si>
+    <t>4. There is no callable orchestration function in Model.dll/Logic.dll at all — the entire pipeline only exists as inline procedural code inside Program.cs's Main.</t>
+  </si>
+  <si>
+    <r>
+      <t>🟢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Lower priority, but worth flagging</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Deployment-target dependencies aren't documented anywhere in code:</t>
+  </si>
+  <si>
+    <t>Windows Registry key (HKEY_CURRENT_USER\Software\XenxibleIdentifier\connectionstring, Program.cs:34-51) must be manually set up on every machine that runs this — there's no installer/setup script for it that I've seen.</t>
+  </si>
+  <si>
+    <t>A working Python environment with the right packages must exist at PYTHON_EXE (env var, defaults to "python" on PATH) — no validation happens before it's used at Program.cs:190; if Python isn't set up right, the failure surfaces deep inside client.RunAsync.</t>
+  </si>
+  <si>
+    <t>SCRIPT_TYPE/SCRIPT_PIPELINE assume the deployed folder structure exactly mirrors your dev repo layout (_projectDir is ..\..\..\ relative to the exe). Any different deployment layout (e.g. published as a standalone folder) breaks this silently.</t>
+  </si>
+  <si>
+    <r>
+      <t>6. The whole app is interactive-only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Console.ReadLine() gating every step, manual-correction loop needing a human typing device IDs) — fine for your own testing, but if this is meant to run unattended (scheduled job, service, API-triggered), none of that exists yet; it would need a non-interactive mode.</t>
+    </r>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>Input (Predict request)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{project_code, customer_code, data_ids} in </t>
+  </si>
+  <si>
+    <t>→ [{customer, data_id, manual_check, data_type, confidence, reason}] out</t>
+  </si>
+  <si>
+    <t>Manual-assign request/response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{action: "user_manual_assign", project_code, customer, assignments: [{data_id, equipment}], batch_results} in </t>
+  </si>
+  <si>
+    <t>→ {status, applied_count, applied} out</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,8 +580,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFEE0000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,8 +645,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -433,11 +660,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -456,19 +735,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5059,7 +5367,15 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = Cluster Prediction</a:t>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>Cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> Prediction</a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
@@ -5307,14 +5623,22 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Quota constraint cluster allocation (Logic)</a:t>
+            <a:t>Quota constraint </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t> allocation (Logic)</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>-  assign by prediction socre</a:t>
+            <a:t>-  assign by prediction score</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6216,9 +6540,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>102119</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126678</xdr:rowOff>
+      <xdr:colOff>119948</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>112025</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6234,7 +6558,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16433831" y="11300236"/>
+          <a:off x="16451660" y="11651929"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6350,15 +6674,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>148834</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>174294</xdr:rowOff>
+      <xdr:colOff>161828</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>18876</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>148834</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126678</xdr:rowOff>
+      <xdr:colOff>179658</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>112025</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6376,9 +6700,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="17088680" y="10981506"/>
-          <a:ext cx="0" cy="318730"/>
+        <a:xfrm>
+          <a:off x="17101674" y="11009261"/>
+          <a:ext cx="17830" cy="642668"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6409,18 +6733,18 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>240928</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>595671</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>67233</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="264560"/>
+      <xdr:rowOff>58775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1828139" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="114" name="TextBox 113">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D11D403-A6F6-4E09-A423-BF14D7C4A436}"/>
+        <xdr:cNvPr id="115" name="TextBox 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D4D37B-5B60-4FB9-BC7D-8F46B08C719E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6428,8 +6752,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19005178" y="10691271"/>
-          <a:ext cx="1329337" cy="264560"/>
+          <a:off x="18745862" y="10637605"/>
+          <a:ext cx="1828139" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6469,13 +6793,16 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Build</a:t>
+            <a:t>unallocated</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> Cluster Group</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>_device_ids</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>.json</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6484,17 +6811,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>240928</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>67233</xdr:rowOff>
+      <xdr:colOff>231904</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>126387</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="115" name="TextBox 114">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D4D37B-5B60-4FB9-BC7D-8F46B08C719E}"/>
+        <xdr:cNvPr id="116" name="TextBox 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBB65AA4-2437-4F0B-B4C6-C1A5489C92FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6502,7 +6829,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19005178" y="10691271"/>
+          <a:off x="18996154" y="11299945"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6543,27 +6870,207 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Dump JSON</a:t>
+            <a:t>Manual correction</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>273055</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>23109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>296958</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>58775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="117" name="Straight Arrow Connector 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2F93E5-A87D-487E-A238-90038BD4B003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="93" idx="2"/>
+          <a:endCxn id="115" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19639204" y="10237152"/>
+          <a:ext cx="23903" cy="400453"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>291769</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>140942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>296958</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123212</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="120" name="Straight Arrow Connector 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC1BA5B-92E6-4618-9BC3-490616DA45ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="115" idx="2"/>
+          <a:endCxn id="116" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="19657918" y="10902165"/>
+          <a:ext cx="5189" cy="347058"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>397423</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>91479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>406199</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>144644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="132" name="Straight Arrow Connector 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{260378DE-440A-4BD2-AD45-A3BDA77E54B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="45" idx="2"/>
+          <a:endCxn id="72" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16810502" y="7671374"/>
+          <a:ext cx="8776" cy="414112"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>231904</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126387</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="264560"/>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>512120</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>65334</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1663960" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="116" name="TextBox 115">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBB65AA4-2437-4F0B-B4C6-C1A5489C92FD}"/>
+        <xdr:cNvPr id="146" name="TextBox 145">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93066E93-A1B2-47F8-A7B6-565C1562B0BF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6571,8 +7078,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18996154" y="11299945"/>
-          <a:ext cx="1329337" cy="264560"/>
+          <a:off x="19786238" y="7954275"/>
+          <a:ext cx="1663960" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6611,9 +7118,10 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Manual correction</a:t>
-          </a:r>
+            <a:rPr lang="en-MY"/>
+            <a:t>floating_deviceid.json</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6621,36 +7129,36 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>271006</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>24021</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>125231</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>68992</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>292394</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>64058</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>133865</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>68509</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="117" name="Straight Arrow Connector 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2F93E5-A87D-487E-A238-90038BD4B003}"/>
+        <xdr:cNvPr id="147" name="Straight Arrow Connector 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5665CFC8-435B-4B29-B9CE-BC0EF0B790F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
-          <a:stCxn id="93" idx="2"/>
-          <a:endCxn id="115" idx="0"/>
+          <a:stCxn id="46" idx="2"/>
+          <a:endCxn id="146" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19698260" y="10212560"/>
-          <a:ext cx="21388" cy="403914"/>
+          <a:off x="20609584" y="7599345"/>
+          <a:ext cx="8634" cy="358105"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6679,140 +7187,20 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>278616</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>141793</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>278616</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126387</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="120" name="Straight Arrow Connector 119">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC1BA5B-92E6-4618-9BC3-490616DA45ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="115" idx="2"/>
-          <a:endCxn id="116" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="19651001" y="10949005"/>
-          <a:ext cx="0" cy="350940"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>397423</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>91479</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>406199</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>144644</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="132" name="Straight Arrow Connector 131">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{260378DE-440A-4BD2-AD45-A3BDA77E54B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="45" idx="2"/>
-          <a:endCxn id="72" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16810502" y="7671374"/>
-          <a:ext cx="8776" cy="414112"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>512120</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>65334</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1663960" cy="264560"/>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>227588</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>12250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="781240"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="146" name="TextBox 145">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93066E93-A1B2-47F8-A7B6-565C1562B0BF}"/>
+        <xdr:cNvPr id="163" name="TextBox 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9969C2D9-5416-4223-9263-1A333080ACB5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6820,8 +7208,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19786238" y="7954275"/>
-          <a:ext cx="1663960" cy="264560"/>
+          <a:off x="19044814" y="11838233"/>
+          <a:ext cx="1329337" cy="781240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6861,136 +7249,6 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY"/>
-            <a:t>floating_deviceid.json</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>125231</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>68992</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>133865</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>68509</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="147" name="Straight Arrow Connector 146">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5665CFC8-435B-4B29-B9CE-BC0EF0B790F6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="46" idx="2"/>
-          <a:endCxn id="146" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20609584" y="7599345"/>
-          <a:ext cx="8634" cy="358105"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>227588</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>12250</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="781240"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="163" name="TextBox 162">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9969C2D9-5416-4223-9263-1A333080ACB5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19044814" y="11838233"/>
-          <a:ext cx="1329337" cy="781240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY"/>
             <a:t>Place into Cluster Group Update JSON Print Updated Section</a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
@@ -7059,6 +7317,143 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>597514</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>160697</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="900824" cy="248851"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="TextBox 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2889AAA-FEAB-64BB-634B-10D732A8CE60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13634858" y="1053666"/>
+          <a:ext cx="900824" cy="248851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1000"/>
+            <a:t>PythonSQL.cs</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>270152</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>41436</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1765548" cy="248851"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="TextBox 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9547220-EF0A-4C2A-8C17-6429A30A6EF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17209998" y="11214994"/>
+          <a:ext cx="1765548" cy="248851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>What</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> is the cluster algorithm?</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8942,47 +9337,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:38" x14ac:dyDescent="0.35">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="N2" s="8" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="N2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="V2" s="8" t="s">
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="V2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AD2" s="8" t="s">
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AD2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="8"/>
-      <c r="AJ2" s="8"/>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="12"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="8"/>
+      <c r="AL2" s="8"/>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.35">
+      <c r="W43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.35">
+      <c r="W44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B48" s="10" t="s">
         <v>5</v>
       </c>
@@ -8990,7 +9395,7 @@
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
     </row>
-    <row r="50" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N50" s="9" t="s">
         <v>11</v>
       </c>
@@ -8998,33 +9403,52 @@
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
       <c r="R50" s="9"/>
+      <c r="V50" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="52" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="14:26" x14ac:dyDescent="0.35">
+      <c r="V51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N52" t="s">
         <v>0</v>
       </c>
+      <c r="V52" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="53" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N53" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N54" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N55" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N56" t="s">
         <v>4</v>
       </c>
+      <c r="V56" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="58" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="14:26" x14ac:dyDescent="0.35">
+      <c r="V57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N58" s="9" t="s">
         <v>23</v>
       </c>
@@ -9033,77 +9457,207 @@
       <c r="Q58" s="9"/>
       <c r="R58" s="9"/>
     </row>
-    <row r="60" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N61" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N63" t="s">
         <v>15</v>
       </c>
+      <c r="V63" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="64" spans="14:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N64" t="s">
         <v>16</v>
       </c>
+      <c r="U64" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+      <c r="Z64" s="14"/>
     </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N65" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N66" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N67" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N68" t="s">
         <v>20</v>
       </c>
+      <c r="V68" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
-    <row r="69" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N69" t="s">
         <v>21</v>
       </c>
+      <c r="V69" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="70" spans="14:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N70" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="AD2:AJ2"/>
     <mergeCell ref="N58:R58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="V2:Z2"/>
     <mergeCell ref="N50:R50"/>
-    <mergeCell ref="AD2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4975E7A9-7752-4B1C-B186-BBC7B2B57660}">
+  <dimension ref="C3:K22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C3" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C4" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C5" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C6" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C7" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C8" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C9" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C10" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C11" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C12" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C13" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C14" s="19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C15" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C16" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="9:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="9:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I20" s="20"/>
+      <c r="J20" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="9:11" ht="224.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I21" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="9:11" ht="304.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I22" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0681933B-6749-4A17-925F-E9EB49A25785}">
   <dimension ref="B2:G29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9468,26 +10022,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55B153B-88FB-4A10-8D3D-E1FB39BC69A3}">
   <dimension ref="B4:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9499,7 +10053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF64B0D-5B81-4205-8202-EA1D03B0667B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A732D-812E-4F4C-BD19-9B58B7EDD54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172331D7-7552-4EE9-A798-6093142F629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
     <sheet name="question" sheetId="5" r:id="rId2"/>
-    <sheet name="Parameter Details" sheetId="3" r:id="rId3"/>
-    <sheet name="Movement dataset" sheetId="2" r:id="rId4"/>
-    <sheet name="suppl" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
+    <sheet name="Parameter Details" sheetId="3" r:id="rId4"/>
+    <sheet name="Movement dataset" sheetId="2" r:id="rId5"/>
+    <sheet name="suppl" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -736,18 +737,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -776,6 +765,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9337,40 +9338,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:38" x14ac:dyDescent="0.35">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="N2" s="11" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="N2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="V2" s="11" t="s">
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="V2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AD2" s="11" t="s">
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AD2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
     </row>
@@ -9388,21 +9389,21 @@
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
     </row>
     <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="9" t="s">
+      <c r="N50" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="21"/>
+      <c r="R50" s="21"/>
       <c r="V50" t="s">
         <v>107</v>
       </c>
@@ -9449,13 +9450,13 @@
       </c>
     </row>
     <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="9" t="s">
+      <c r="N58" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9"/>
+      <c r="O58" s="21"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="21"/>
+      <c r="R58" s="21"/>
     </row>
     <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -9484,14 +9485,14 @@
       <c r="N64" t="s">
         <v>16</v>
       </c>
-      <c r="U64" s="13" t="s">
+      <c r="U64" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V64" s="14"/>
-      <c r="W64" s="14"/>
-      <c r="X64" s="14"/>
-      <c r="Y64" s="14"/>
-      <c r="Z64" s="14"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="10"/>
+      <c r="Y64" s="10"/>
+      <c r="Z64" s="10"/>
     </row>
     <row r="65" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N65" t="s">
@@ -9547,109 +9548,77 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4975E7A9-7752-4B1C-B186-BBC7B2B57660}">
-  <dimension ref="C3:K22"/>
+  <dimension ref="C3:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="11" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="5" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="12" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="11" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="15" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="15" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="15" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="16" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="12" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="9:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="9:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I20" s="20"/>
-      <c r="J20" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="9:11" ht="224.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I21" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="9:11" ht="304.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I22" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -9658,6 +9627,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DCE81F-EE57-4F7E-9711-CBC0F05A507F}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43.26953125" customWidth="1"/>
+    <col min="3" max="3" width="45.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="16"/>
+      <c r="B1" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0681933B-6749-4A17-925F-E9EB49A25785}">
   <dimension ref="B2:G29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9671,14 +9686,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -9781,14 +9796,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -10022,26 +10037,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55B153B-88FB-4A10-8D3D-E1FB39BC69A3}">
   <dimension ref="B4:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10053,7 +10068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF64B0D-5B81-4205-8202-EA1D03B0667B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172331D7-7552-4EE9-A798-6093142F629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -766,6 +766,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -774,9 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9338,40 +9338,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:38" x14ac:dyDescent="0.35">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="N2" s="20" t="s">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="N2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="V2" s="20" t="s">
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="V2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AD2" s="20" t="s">
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AD2" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
     </row>
@@ -9389,21 +9389,21 @@
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
     </row>
     <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="21" t="s">
+      <c r="N50" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="21"/>
-      <c r="R50" s="21"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="22"/>
       <c r="V50" t="s">
         <v>107</v>
       </c>
@@ -9450,13 +9450,13 @@
       </c>
     </row>
     <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="21" t="s">
+      <c r="N58" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22"/>
+      <c r="R58" s="22"/>
     </row>
     <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -9686,14 +9686,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -9796,14 +9796,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -10043,20 +10043,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172331D7-7552-4EE9-A798-6093142F629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F12C684-0200-47C1-943E-A529E9043FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -766,9 +766,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -777,6 +774,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6793,15 +6793,33 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
             <a:t>unallocated</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
             <a:t>_device_ids</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
             <a:t>.json</a:t>
           </a:r>
         </a:p>
@@ -7119,10 +7137,22 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY"/>
+            <a:rPr lang="en-MY" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
             <a:t>floating_deviceid.json</a:t>
           </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+          <a:endParaRPr lang="en-MY" sz="1100" b="1" u="none">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9338,40 +9368,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:38" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="N2" s="21" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="N2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="V2" s="21" t="s">
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="V2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AD2" s="21" t="s">
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AD2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
     </row>
@@ -9389,21 +9419,21 @@
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
     </row>
     <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="22" t="s">
+      <c r="N50" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
+      <c r="O50" s="21"/>
+      <c r="P50" s="21"/>
+      <c r="Q50" s="21"/>
+      <c r="R50" s="21"/>
       <c r="V50" t="s">
         <v>107</v>
       </c>
@@ -9450,13 +9480,13 @@
       </c>
     </row>
     <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="22" t="s">
+      <c r="N58" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="22"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="22"/>
-      <c r="R58" s="22"/>
+      <c r="O58" s="21"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="21"/>
+      <c r="R58" s="21"/>
     </row>
     <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -9686,14 +9716,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -9796,14 +9826,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -10043,20 +10073,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F12C684-0200-47C1-943E-A529E9043FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAED232-06D5-4F65-98FA-D106F1199A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="139">
   <si>
     <t>ALPHA_PREFIX_WEIGHT     = 0.65</t>
   </si>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t>→ {status, applied_count, applied} out</t>
+  </si>
+  <si>
+    <t>dbo.DeviceReviewQueue</t>
   </si>
 </sst>
 </file>
@@ -3130,7 +3133,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>133882</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>25762</xdr:rowOff>
+      <xdr:rowOff>28937</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3179,7 +3182,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>105</xdr:row>
-      <xdr:rowOff>26862</xdr:rowOff>
+      <xdr:rowOff>30037</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3226,7 +3229,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>105465</xdr:colOff>
+      <xdr:colOff>102290</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>57699</xdr:rowOff>
     </xdr:to>
@@ -3275,9 +3278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>387351</xdr:colOff>
+      <xdr:colOff>390526</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>144957</xdr:rowOff>
+      <xdr:rowOff>141782</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4476,7 +4479,7 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>28258</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1732998" cy="264560"/>
+    <xdr:ext cx="1732998" cy="436786"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="TextBox 2">
@@ -4490,8 +4493,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17959912" y="760950"/>
-          <a:ext cx="1732998" cy="264560"/>
+          <a:off x="17969682" y="770720"/>
+          <a:ext cx="1732998" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4534,8 +4537,23 @@
             <a:t>Source Dataset : </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>DB SQL</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(dbo.DummyTestingData)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4928,16 +4946,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>24976</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>114224</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>606796</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>93814</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>24976</xdr:colOff>
+      <xdr:colOff>20843</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>75867</xdr:rowOff>
+      <xdr:rowOff>79042</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4955,8 +4973,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18855168" y="1030089"/>
-          <a:ext cx="0" cy="327990"/>
+          <a:off x="18836181" y="1207506"/>
+          <a:ext cx="24624" cy="170844"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5670,9 +5688,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>227148</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>166469</xdr:rowOff>
+      <xdr:colOff>293601</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>163294</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3522340" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -5688,7 +5706,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17214290" y="12902143"/>
+          <a:off x="17364764" y="14376957"/>
           <a:ext cx="3522340" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6467,9 +6485,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>102118</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123838</xdr:rowOff>
+      <xdr:colOff>98131</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>174209</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6485,7 +6503,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16433830" y="10747876"/>
+          <a:off x="16417631" y="11422780"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6541,9 +6559,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>119948</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>112025</xdr:rowOff>
+      <xdr:colOff>81964</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6559,7 +6577,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16451660" y="11651929"/>
+          <a:off x="16479618" y="12374015"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6615,15 +6633,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>159695</xdr:colOff>
+      <xdr:colOff>146039</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>88110</xdr:rowOff>
+      <xdr:rowOff>47371</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>159695</xdr:colOff>
+      <xdr:colOff>163897</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>142888</xdr:rowOff>
+      <xdr:rowOff>107608</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6637,13 +6655,13 @@
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
           <a:stCxn id="90" idx="2"/>
-          <a:endCxn id="98" idx="0"/>
+          <a:endCxn id="56" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17099541" y="10345802"/>
-          <a:ext cx="0" cy="421124"/>
+        <a:xfrm flipH="1">
+          <a:off x="17154270" y="10441833"/>
+          <a:ext cx="17858" cy="431467"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6675,15 +6693,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>161828</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>18876</xdr:rowOff>
+      <xdr:colOff>136056</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>67538</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>179658</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>112025</xdr:rowOff>
+      <xdr:colOff>152223</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6701,9 +6719,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17101674" y="11009261"/>
-          <a:ext cx="17830" cy="642668"/>
+        <a:xfrm flipH="1">
+          <a:off x="17144287" y="11946923"/>
+          <a:ext cx="16167" cy="427092"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6739,7 +6757,7 @@
       <xdr:row>58</xdr:row>
       <xdr:rowOff>58775</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1828139" cy="264560"/>
+    <xdr:ext cx="1828139" cy="436786"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="115" name="TextBox 114">
@@ -6753,8 +6771,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18745862" y="10637605"/>
-          <a:ext cx="1828139" cy="264560"/>
+          <a:off x="18883671" y="10891128"/>
+          <a:ext cx="1828139" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6823,6 +6841,17 @@
             <a:t>.json</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(dbo.DeviceReviewQueue)</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -6899,13 +6928,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>273055</xdr:colOff>
+      <xdr:colOff>265271</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>23109</xdr:rowOff>
+      <xdr:rowOff>17542</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>296958</xdr:colOff>
+      <xdr:colOff>284565</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>58775</xdr:rowOff>
     </xdr:to>
@@ -6926,8 +6955,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19639204" y="10237152"/>
-          <a:ext cx="23903" cy="400453"/>
+          <a:off x="19778447" y="10476366"/>
+          <a:ext cx="19294" cy="414762"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6959,15 +6988,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>291769</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>140942</xdr:rowOff>
+      <xdr:colOff>283985</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>122032</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>296958</xdr:colOff>
+      <xdr:colOff>284565</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>123212</xdr:rowOff>
+      <xdr:rowOff>126387</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6986,8 +7015,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19657918" y="10902165"/>
-          <a:ext cx="5189" cy="347058"/>
+          <a:off x="19797161" y="11327914"/>
+          <a:ext cx="580" cy="191120"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7411,11 +7440,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>270152</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>41436</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1765548" cy="248851"/>
+      <xdr:colOff>244678</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>104909</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1762376" cy="248851"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="63" name="TextBox 62">
@@ -7429,8 +7458,194 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17209998" y="11214994"/>
-          <a:ext cx="1765548" cy="248851"/>
+          <a:off x="17199178" y="11643766"/>
+          <a:ext cx="1762376" cy="248851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>What</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> is the cluster algorithm?</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1000" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>263769</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>107608</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2206847" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B3D162-6C18-4078-A83C-275CF136E2BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16050846" y="10873300"/>
+          <a:ext cx="2206847" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Matching</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t> pattern cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>DB SQL</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(dbo.PatternCluster)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>266665</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>138978</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="900824" cy="248851"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="TextBox 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D008A83F-C7DB-460A-B447-086CAF236E10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17264460" y="10322069"/>
+          <a:ext cx="900824" cy="248851"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7460,22 +7675,167 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-MY" sz="1000" b="1">
+            <a:rPr lang="en-MY" sz="1000"/>
+            <a:t>PythonSQL.cs</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>146039</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>173163</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>152223</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>174209</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="75" name="Straight Arrow Connector 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CAF7F83-362C-4E2A-8ED0-57AC6B83768E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="56" idx="2"/>
+          <a:endCxn id="98" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17154270" y="11310086"/>
+          <a:ext cx="6184" cy="372277"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>399545</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>160738</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1911184" cy="436786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="TextBox 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B60B1F7-735E-40B3-A9F8-2E8E9CDBF9B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16186622" y="13153815"/>
+          <a:ext cx="1911184" cy="436786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Output </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>What</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1000" b="1" baseline="0">
+            <a:t>DB SQL. HANGING.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> is the cluster algorithm?</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1000" b="1">
+            <a:t> NOT START YET</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none">
             <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
@@ -7485,6 +7845,66 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>133983</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>16729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>136056</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>160738</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="91" name="Straight Arrow Connector 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{458E7907-37C5-41F7-829F-D221614388E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="99" idx="2"/>
+          <a:endCxn id="89" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="17142214" y="12638575"/>
+          <a:ext cx="2073" cy="515240"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9358,7 +9778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="B2:AL70"/>
+  <dimension ref="B2:AL84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
@@ -9558,6 +9978,11 @@
     <row r="70" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N70" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="33:33" x14ac:dyDescent="0.35">
+      <c r="AG84" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAED232-06D5-4F65-98FA-D106F1199A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D0C432-E5EB-4FB0-91F0-3110121F7257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -720,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -739,7 +739,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4474,8 +4473,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>350874</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>608506</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>28258</xdr:rowOff>
     </xdr:from>
@@ -4493,7 +4492,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17969682" y="770720"/>
+          <a:off x="19481613" y="735829"/>
           <a:ext cx="1732998" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4542,7 +4541,7 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>DB SQL</a:t>
+            <a:t> </a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4553,7 +4552,23 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>(dbo.DummyTestingData)</a:t>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dbo.DummyTestingData</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4562,8 +4577,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>101453</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>394010</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>79042</xdr:rowOff>
     </xdr:from>
@@ -4581,7 +4596,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18321068" y="1361254"/>
+          <a:off x="19879439" y="1317292"/>
           <a:ext cx="1059934" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4636,8 +4651,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>408421</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>53731</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>26656</xdr:rowOff>
     </xdr:from>
@@ -4655,7 +4670,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18017459" y="2041560"/>
+          <a:off x="19539160" y="1972477"/>
           <a:ext cx="1732998" cy="437873"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4717,8 +4732,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>330633</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>600965</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>25862</xdr:rowOff>
     </xdr:from>
@@ -4736,7 +4751,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17939671" y="3506150"/>
+          <a:off x="19474072" y="3386826"/>
           <a:ext cx="1732998" cy="437873"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4798,8 +4813,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>100107</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>360914</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>18196</xdr:rowOff>
     </xdr:from>
@@ -4817,7 +4832,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17709145" y="4231177"/>
+          <a:off x="19234021" y="4086732"/>
           <a:ext cx="2247541" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4862,7 +4877,15 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = Section Prediction</a:t>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>Section</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> Prediction</a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
@@ -4872,8 +4895,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>235342</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>489799</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>133686</xdr:rowOff>
     </xdr:from>
@@ -4891,7 +4914,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17844380" y="2881282"/>
+          <a:off x="19362906" y="2787079"/>
           <a:ext cx="2071535" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4946,14 +4969,14 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>606796</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>255282</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>93814</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>20843</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>265775</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>79042</xdr:rowOff>
     </xdr:to>
@@ -4973,8 +4996,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18836181" y="1207506"/>
-          <a:ext cx="24624" cy="170844"/>
+          <a:off x="20353032" y="1155171"/>
+          <a:ext cx="10493" cy="162121"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5005,14 +5028,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>25373</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>317930</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>161833</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>25373</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>317930</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>20306</xdr:rowOff>
     </xdr:to>
@@ -5032,8 +5055,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18855565" y="1627218"/>
-          <a:ext cx="0" cy="407992"/>
+          <a:off x="20415680" y="1576976"/>
+          <a:ext cx="0" cy="389151"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5064,14 +5087,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>6761</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>261218</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>107341</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>6761</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>261218</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>140036</xdr:rowOff>
     </xdr:to>
@@ -5091,8 +5114,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18836953" y="2488591"/>
-          <a:ext cx="0" cy="399041"/>
+          <a:off x="20358968" y="2406948"/>
+          <a:ext cx="0" cy="386481"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5123,14 +5146,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>4735</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>246492</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>37883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>4735</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>246492</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>19512</xdr:rowOff>
     </xdr:to>
@@ -5150,8 +5173,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18834927" y="3151825"/>
-          <a:ext cx="0" cy="347975"/>
+          <a:off x="20344242" y="3045062"/>
+          <a:ext cx="0" cy="335414"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5182,14 +5205,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>4735</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>246492</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>103372</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>4735</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>246492</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>21371</xdr:rowOff>
     </xdr:to>
@@ -5209,8 +5232,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18834927" y="3950007"/>
-          <a:ext cx="0" cy="284345"/>
+          <a:off x="20344242" y="3818122"/>
+          <a:ext cx="0" cy="271785"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5241,8 +5264,8 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>347303</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>611285</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>10080</xdr:rowOff>
     </xdr:from>
@@ -5260,7 +5283,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17956341" y="4772580"/>
+          <a:off x="19484392" y="4609294"/>
           <a:ext cx="1732998" cy="437873"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5301,7 +5324,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
-            <a:t>Section </a:t>
+            <a:t>Cluster </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
@@ -5322,8 +5345,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>82583</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>375140</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>20433</xdr:rowOff>
     </xdr:from>
@@ -5341,7 +5364,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17691621" y="5515625"/>
+          <a:off x="19248247" y="5327219"/>
           <a:ext cx="2247541" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5404,14 +5427,14 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>5530</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>282212</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>107337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>5530</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>282212</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>10780</xdr:rowOff>
     </xdr:to>
@@ -5431,8 +5454,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18835722" y="4503491"/>
-          <a:ext cx="0" cy="269789"/>
+          <a:off x="20379962" y="4352766"/>
+          <a:ext cx="0" cy="257228"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5463,14 +5486,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>23664</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>265421</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>97816</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>23664</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>265421</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>26783</xdr:rowOff>
     </xdr:to>
@@ -5490,8 +5513,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18853856" y="5226662"/>
-          <a:ext cx="0" cy="295313"/>
+          <a:off x="20363171" y="5050816"/>
+          <a:ext cx="0" cy="282753"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5522,14 +5545,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>602231</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>273108</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>106000</xdr:rowOff>
+      <xdr:rowOff>105379</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>15575</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>276536</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>88834</xdr:rowOff>
     </xdr:to>
@@ -5549,9 +5572,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18725301" y="5654792"/>
-          <a:ext cx="20643" cy="340821"/>
+        <a:xfrm flipH="1">
+          <a:off x="20291937" y="5673422"/>
+          <a:ext cx="3428" cy="342683"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5582,10 +5605,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>468149</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>126161</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>88834</xdr:rowOff>
+      <xdr:rowOff>85659</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2738644" cy="991518"/>
     <xdr:sp macro="" textlink="">
@@ -5601,7 +5624,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17376622" y="5995613"/>
+          <a:off x="18925790" y="6012930"/>
           <a:ext cx="2738644" cy="991518"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5641,16 +5664,24 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
             <a:t>Quota constraint </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
             <a:t>cluster</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t> allocation (Logic)</a:t>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
+            <a:t> allocation (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
+            <a:t>Logic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
+            <a:t>)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -5773,8 +5804,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>344359</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>589291</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>10568</xdr:rowOff>
     </xdr:from>
@@ -5792,7 +5823,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16180707" y="7481481"/>
+          <a:off x="17625434" y="7263175"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5843,8 +5874,8 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>68855</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>326487</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>159845</xdr:rowOff>
     </xdr:from>
@@ -5862,7 +5893,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20151566" y="7378792"/>
+          <a:off x="21648880" y="7235559"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5912,16 +5943,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>396115</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>34760</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>34766</xdr:rowOff>
+      <xdr:rowOff>45749</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>464974</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>122986</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>7393</xdr:rowOff>
+      <xdr:rowOff>7392</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5939,8 +5970,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="16845376" y="6594592"/>
-          <a:ext cx="681772" cy="883714"/>
+          <a:off x="18224789" y="6511863"/>
+          <a:ext cx="697826" cy="859715"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -5971,14 +6002,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>155618</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>423230</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>38493</xdr:rowOff>
+      <xdr:rowOff>45750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>120749</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>381556</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>163020</xdr:rowOff>
     </xdr:to>
@@ -5998,8 +6029,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20177168" y="6553593"/>
-          <a:ext cx="574731" cy="848427"/>
+          <a:off x="21661259" y="6511864"/>
+          <a:ext cx="567926" cy="835727"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6030,8 +6061,8 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>349960</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>610767</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>141469</xdr:rowOff>
     </xdr:from>
@@ -6049,7 +6080,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16151434" y="8082311"/>
+          <a:off x="17646910" y="7924755"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6089,7 +6120,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
             <a:t>Logic.dll</a:t>
           </a:r>
         </a:p>
@@ -6168,14 +6199,14 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>406199</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>39665</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>48257</xdr:rowOff>
+      <xdr:rowOff>55419</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>41097</xdr:colOff>
+      <xdr:colOff>50793</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>105656</xdr:rowOff>
     </xdr:to>
@@ -6195,9 +6226,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16819278" y="8350046"/>
-          <a:ext cx="1469714" cy="779294"/>
+        <a:xfrm flipH="1">
+          <a:off x="18300451" y="8192490"/>
+          <a:ext cx="11128" cy="757809"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6485,9 +6516,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>98131</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>174209</xdr:rowOff>
+      <xdr:colOff>78079</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>134104</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6503,7 +6534,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16417631" y="11422780"/>
+          <a:off x="16491158" y="11503946"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6559,9 +6590,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>81964</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123400</xdr:rowOff>
+      <xdr:colOff>80126</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>101509</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6577,7 +6608,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16479618" y="12374015"/>
+          <a:off x="16493205" y="12193246"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6633,13 +6664,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>146039</xdr:colOff>
+      <xdr:colOff>141367</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>47371</xdr:rowOff>
+      <xdr:rowOff>54167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>163897</xdr:colOff>
+      <xdr:colOff>158386</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>107608</xdr:rowOff>
     </xdr:to>
@@ -6660,8 +6691,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17154270" y="10441833"/>
-          <a:ext cx="17858" cy="431467"/>
+          <a:off x="17203541" y="10258341"/>
+          <a:ext cx="17019" cy="417876"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6693,15 +6724,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>136056</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>67538</xdr:rowOff>
+      <xdr:colOff>131143</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>37717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>152223</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123400</xdr:rowOff>
+      <xdr:colOff>136365</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>104684</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6719,9 +6750,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="17144287" y="11946923"/>
-          <a:ext cx="16167" cy="427092"/>
+        <a:xfrm>
+          <a:off x="17155827" y="11768506"/>
+          <a:ext cx="5222" cy="427915"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6771,7 +6802,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18883671" y="10891128"/>
+          <a:off x="18769809" y="10726775"/>
           <a:ext cx="1828139" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6849,7 +6880,23 @@
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>(dbo.DeviceReviewQueue)</a:t>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>dbo.DeviceReviewQueue</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -7047,14 +7094,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>397423</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>32133</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>91479</xdr:rowOff>
+      <xdr:rowOff>88022</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>406199</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>53609</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>144644</xdr:rowOff>
     </xdr:to>
@@ -7075,8 +7122,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16810502" y="7671374"/>
-          <a:ext cx="8776" cy="414112"/>
+          <a:off x="18267581" y="7813125"/>
+          <a:ext cx="21476" cy="424485"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7107,10 +7154,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>512120</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>142288</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>65334</xdr:rowOff>
+      <xdr:rowOff>97817</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1663960" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -7126,7 +7173,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19786238" y="7954275"/>
+          <a:off x="21339076" y="8157432"/>
           <a:ext cx="1663960" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7189,16 +7236,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>125231</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>369308</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>68992</xdr:rowOff>
+      <xdr:rowOff>61234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>133865</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>383021</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>68509</xdr:rowOff>
+      <xdr:rowOff>97817</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7216,9 +7263,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20609584" y="7599345"/>
-          <a:ext cx="8634" cy="358105"/>
+        <a:xfrm flipH="1">
+          <a:off x="22174231" y="7754503"/>
+          <a:ext cx="13713" cy="402929"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7440,9 +7487,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>244678</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>104909</xdr:rowOff>
+      <xdr:colOff>207749</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>126801</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1762376" cy="248851"/>
     <xdr:sp macro="" textlink="">
@@ -7458,7 +7505,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17199178" y="11643766"/>
+          <a:off x="17232433" y="11857590"/>
           <a:ext cx="1762376" cy="248851"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7519,9 +7566,9 @@
       <xdr:col>28</xdr:col>
       <xdr:colOff>263769</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>107608</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2206847" cy="436786"/>
+      <xdr:rowOff>104433</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2206847" cy="609013"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="56" name="TextBox 55">
@@ -7535,8 +7582,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16050846" y="10873300"/>
-          <a:ext cx="2206847" cy="436786"/>
+          <a:off x="16100117" y="10673042"/>
+          <a:ext cx="2206847" cy="609013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7586,18 +7633,15 @@
             <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
             <a:t>: </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>DB SQL</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7611,13 +7655,43 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>(dbo.PatternCluster)</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>dbo.PatternCluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>*any modification pattern  is here</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7686,15 +7760,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>146039</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>173163</xdr:rowOff>
+      <xdr:colOff>131143</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>175200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>152223</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>174209</xdr:rowOff>
+      <xdr:colOff>143983</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>134104</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7712,9 +7786,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17154270" y="11310086"/>
-          <a:ext cx="6184" cy="372277"/>
+        <a:xfrm flipH="1">
+          <a:off x="17155827" y="11184095"/>
+          <a:ext cx="12840" cy="319851"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7746,11 +7820,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>399545</xdr:colOff>
+      <xdr:colOff>281303</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>160738</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1911184" cy="436786"/>
+      <xdr:rowOff>151979</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2149214" cy="434849"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="89" name="TextBox 88">
@@ -7764,8 +7838,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16186622" y="13153815"/>
-          <a:ext cx="1911184" cy="436786"/>
+          <a:off x="16020544" y="13027151"/>
+          <a:ext cx="2149214" cy="434849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7798,11 +7872,27 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
+          <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
             <a:t>Output </a:t>
@@ -7813,6 +7903,18 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -7821,10 +7923,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>DB SQL. HANGING.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" baseline="0">
+            <a:t>dbo.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -7833,8 +7935,26 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> NOT START YET</a:t>
-          </a:r>
+            <a:t>OutputDeviceAssignment</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none">
             <a:solidFill>
               <a:srgbClr val="FF0000"/>
@@ -7848,15 +7968,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>133983</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>16729</xdr:rowOff>
+      <xdr:colOff>129525</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>8297</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>136056</xdr:colOff>
+      <xdr:colOff>136365</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>160738</xdr:rowOff>
+      <xdr:rowOff>151979</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7875,8 +7995,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17142214" y="12638575"/>
-          <a:ext cx="2073" cy="515240"/>
+          <a:off x="17154209" y="12460981"/>
+          <a:ext cx="6840" cy="324156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -9778,7 +9898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="B2:AL84"/>
+  <dimension ref="B2:AP84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
@@ -9787,45 +9907,49 @@
     <col min="28" max="28" width="2.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38" x14ac:dyDescent="0.35">
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="2:42" x14ac:dyDescent="0.35">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="N2" s="20" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="N2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="V2" s="20" t="s">
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="V2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AD2" s="20" t="s">
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AD2" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="8"/>
-      <c r="AL2" s="8"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
     </row>
-    <row r="15" spans="2:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:42" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.35">
@@ -9839,21 +9963,21 @@
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="21" t="s">
+      <c r="N50" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="21"/>
-      <c r="R50" s="21"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
       <c r="V50" t="s">
         <v>107</v>
       </c>
@@ -9900,13 +10024,13 @@
       </c>
     </row>
     <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="21" t="s">
+      <c r="N58" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
     </row>
     <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -9935,14 +10059,14 @@
       <c r="N64" t="s">
         <v>16</v>
       </c>
-      <c r="U64" s="9" t="s">
+      <c r="U64" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="10"/>
-      <c r="Z64" s="10"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="9"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="9"/>
+      <c r="Z64" s="9"/>
     </row>
     <row r="65" spans="14:22" x14ac:dyDescent="0.35">
       <c r="N65" t="s">
@@ -9987,13 +10111,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AD2:AJ2"/>
     <mergeCell ref="N58:R58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="V2:Z2"/>
     <mergeCell ref="N50:R50"/>
+    <mergeCell ref="AD2:AP2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10007,72 +10131,72 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="5" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="11" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="16" spans="3:3" ht="16" x14ac:dyDescent="0.35">
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>129</v>
       </c>
     </row>
@@ -10092,33 +10216,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>137</v>
       </c>
     </row>
@@ -10141,14 +10265,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -10251,14 +10375,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -10498,20 +10622,20 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="4" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="17" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D0C432-E5EB-4FB0-91F0-3110121F7257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41250020-B058-42D0-876A-187674F05510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -277,9 +277,6 @@
     <t>allows each tree to use 80% of the available features.</t>
   </si>
   <si>
-    <t>Current Workflow Application [06/08/2026]</t>
-  </si>
-  <si>
     <t>PARAMETER SGD Classifier</t>
   </si>
   <si>
@@ -546,6 +543,9 @@
   </si>
   <si>
     <t>dbo.DeviceReviewQueue</t>
+  </si>
+  <si>
+    <t>Current Workflow Application [28/08/2026]</t>
   </si>
 </sst>
 </file>
@@ -768,14 +768,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4473,10 +4473,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>608506</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>28258</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>61092</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85189</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1732998" cy="436786"/>
     <xdr:sp macro="" textlink="">
@@ -4492,7 +4492,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19481613" y="735829"/>
+          <a:off x="19452678" y="636982"/>
           <a:ext cx="1732998" cy="436786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4578,9 +4578,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>394010</xdr:colOff>
+      <xdr:colOff>398389</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>79042</xdr:rowOff>
+      <xdr:rowOff>87801</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1059934" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -4596,7 +4596,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19879439" y="1317292"/>
+          <a:off x="19789975" y="1375318"/>
           <a:ext cx="1059934" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4722,7 +4722,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = SGD Classifier</a:t>
+            <a:t> = Binary Rule-Based</a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
@@ -4732,10 +4732,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>600965</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>25862</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>53551</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>179139</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1732998" cy="437873"/>
     <xdr:sp macro="" textlink="">
@@ -4751,7 +4751,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19474072" y="3386826"/>
+          <a:off x="19445137" y="2754173"/>
           <a:ext cx="1732998" cy="437873"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4811,20 +4811,198 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>318867</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>154113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>319632</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>87801</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17343C1B-A944-44E4-9EC0-B420EBBFC051}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20319177" y="1073768"/>
+          <a:ext cx="765" cy="301550"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>311506</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>168430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>319632</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>26656</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EF53A86-F7F4-4B19-B9CD-ECE855001D8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="20311816" y="1639878"/>
+          <a:ext cx="8126" cy="410019"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>311326</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>96667</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>311506</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>179139</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552185D7-9883-4C8A-AD32-88509CDA745C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="7" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="20311636" y="2487770"/>
+          <a:ext cx="180" cy="266403"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>360914</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>18196</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2247541" cy="264560"/>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>55112</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>176493</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1732998" cy="437873"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="TextBox 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1D28F6-3E54-4D76-BB37-95566F56EFBB}"/>
+        <xdr:cNvPr id="28" name="TextBox 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD7B8EA4-5E3B-4906-94B5-FA62524547E7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4832,8 +5010,362 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19234021" y="4086732"/>
-          <a:ext cx="2247541" cy="264560"/>
+          <a:off x="19446698" y="3487252"/>
+          <a:ext cx="1732998" cy="437873"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Cluster </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
+            <a:t>Prediction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
+            <a:t> = XGBoost</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>311326</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>65218</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>312887</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>176493</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Arrow Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837ACBE4-0B47-46F9-B93E-5E098929F978}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="28" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20311636" y="3192046"/>
+          <a:ext cx="1561" cy="295206"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>310423</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>66678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>321281</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>107555</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Straight Arrow Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F95938D-72F4-4584-ADFB-AB4C15451554}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="28" idx="2"/>
+          <a:endCxn id="36" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20384361" y="3900491"/>
+          <a:ext cx="10858" cy="406002"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>174334</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>107555</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2738644" cy="1110851"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="TextBox 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D34A4554-806B-4E8D-B0B4-0A6F122F7467}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19025897" y="4306493"/>
+          <a:ext cx="2738644" cy="1110851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
+            <a:t>Quota constraint </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
+            <a:t>cluster</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
+            <a:t> allocation (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
+            <a:t>Logic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>-  assign by prediction score</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Find exceeded / vacant clusters.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>xcess devices kicked out to reassignment pool</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Device-centric reassignment</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>293601</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>163294</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3522340" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="TextBox 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A8F4F18-C6CF-4495-BF31-5F2989416B90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17364764" y="14376957"/>
+          <a:ext cx="3522340" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4872,22 +5404,26 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Output</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
-            <a:t>Section</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> Prediction</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>list of unknown [PENDING - no</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> output in console apps]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100" b="1" u="none">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4895,18 +5431,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>489799</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>133686</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2071535" cy="264560"/>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>15599</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>180813</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D17522-3EAF-4369-B79B-692AC03FA7C7}"/>
+        <xdr:cNvPr id="45" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5E555AA-BB00-4922-829D-22E57D299727}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4914,8 +5450,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19362906" y="2787079"/>
-          <a:ext cx="2071535" cy="264560"/>
+          <a:off x="17581013" y="5698744"/>
+          <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4954,12 +5490,8 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Output</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = Device Type Prediction</a:t>
+            <a:rPr lang="en-MY"/>
+            <a:t>Assigned Devices </a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
@@ -4967,315 +5499,20 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>255282</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>93814</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>265775</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>79042</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17343C1B-A944-44E4-9EC0-B420EBBFC051}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20353032" y="1155171"/>
-          <a:ext cx="10493" cy="162121"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>317930</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>161833</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>317930</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>20306</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EF53A86-F7F4-4B19-B9CD-ECE855001D8F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="6" idx="2"/>
-          <a:endCxn id="7" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20415680" y="1576976"/>
-          <a:ext cx="0" cy="389151"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>261218</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>107341</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>261218</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>140036</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="Straight Arrow Connector 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{504E1941-06EF-46C0-9FB7-AF74991E0A48}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="2"/>
-          <a:endCxn id="11" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20358968" y="2406948"/>
-          <a:ext cx="0" cy="386481"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>246492</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>37883</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>246492</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>19512</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{552185D7-9883-4C8A-AD32-88509CDA745C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="2"/>
-          <a:endCxn id="9" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20344242" y="3045062"/>
-          <a:ext cx="0" cy="335414"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>246492</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>103372</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>246492</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>21371</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="Straight Arrow Connector 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7064886-E837-4C16-8CC4-C1AB444A903C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="2"/>
-          <a:endCxn id="10" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20344242" y="3818122"/>
-          <a:ext cx="0" cy="271785"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>611285</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1732998" cy="437873"/>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>344004</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47623</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="TextBox 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD7B8EA4-5E3B-4906-94B5-FA62524547E7}"/>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65BCA9D0-56BA-46A4-9E3A-F464272C48E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5283,89 +5520,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19484392" y="4609294"/>
-          <a:ext cx="1732998" cy="437873"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
-            <a:t>Cluster </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
-            <a:t>Prediction</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = XGBoost</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>375140</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>20433</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2247541" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="TextBox 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B2B07A3-95A2-40C9-B913-C6CC0F12FD82}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19248247" y="5327219"/>
-          <a:ext cx="2247541" cy="264560"/>
+          <a:off x="21561763" y="5749485"/>
+          <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5405,21 +5561,8 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>Output</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> = </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0"/>
-            <a:t>Cluster</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none" baseline="0"/>
-            <a:t> Prediction</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
+            <a:t>floating cluster</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5427,532 +5570,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>282212</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>107337</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>282212</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>71544</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>10780</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="Straight Arrow Connector 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837ACBE4-0B47-46F9-B93E-5E098929F978}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="10" idx="2"/>
-          <a:endCxn id="28" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20379962" y="4352766"/>
-          <a:ext cx="0" cy="257228"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>265421</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>97816</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>265421</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>26783</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Straight Arrow Connector 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21A39095-5ED9-49D9-ACD5-3DD6C013A85C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="28" idx="2"/>
-          <a:endCxn id="29" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20363171" y="5050816"/>
-          <a:ext cx="0" cy="282753"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>273108</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>105379</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>276536</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>88834</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Straight Arrow Connector 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F95938D-72F4-4584-ADFB-AB4C15451554}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="29" idx="2"/>
-          <a:endCxn id="36" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="20291937" y="5673422"/>
-          <a:ext cx="3428" cy="342683"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>126161</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>85659</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2738644" cy="991518"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="TextBox 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D34A4554-806B-4E8D-B0B4-0A6F122F7467}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18925790" y="6012930"/>
-          <a:ext cx="2738644" cy="991518"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
-            <a:t>Quota constraint </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
-            <a:t>cluster</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
-            <a:t> allocation (</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="sng"/>
-            <a:t>Logic</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="sng"/>
-            <a:t>)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>-  assign by prediction score</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>- check cluster score</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>- resolve exceeded/vacant cluster</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>- create floating devices</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>293601</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>163294</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3522340" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="TextBox 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A8F4F18-C6CF-4495-BF31-5F2989416B90}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17364764" y="14376957"/>
-          <a:ext cx="3522340" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>list of unknown [PENDING - no</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> output in console apps]</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="1" u="none">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>589291</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>10568</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="TextBox 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5E555AA-BB00-4922-829D-22E57D299727}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17625434" y="7263175"/>
-          <a:ext cx="1329337" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY"/>
-            <a:t>Assigned Devices </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>326487</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>159845</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="TextBox 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65BCA9D0-56BA-46A4-9E3A-F464272C48E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21648880" y="7235559"/>
-          <a:ext cx="1329337" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="0" u="none"/>
-            <a:t>floating cluster</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>34760</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>45749</xdr:rowOff>
+      <xdr:rowOff>111187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>122986</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>7392</xdr:rowOff>
+      <xdr:colOff>174334</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>180812</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5970,8 +5597,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="18224789" y="6511863"/>
-          <a:ext cx="697826" cy="859715"/>
+          <a:off x="18245682" y="4893394"/>
+          <a:ext cx="711514" cy="805349"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6003,15 +5630,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>37</xdr:col>
-      <xdr:colOff>423230</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>45750</xdr:rowOff>
+      <xdr:colOff>478081</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>111188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>381556</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>163020</xdr:rowOff>
+      <xdr:colOff>399949</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47623</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6029,8 +5656,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21661259" y="6511864"/>
-          <a:ext cx="567926" cy="835727"/>
+          <a:off x="21695840" y="4893395"/>
+          <a:ext cx="530592" cy="856090"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6061,10 +5688,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>610767</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>141469</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>20654</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>182744</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6080,7 +5707,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17646910" y="7924755"/>
+          <a:off x="17586068" y="6252468"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6131,9 +5758,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>426765</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>102481</xdr:rowOff>
+      <xdr:colOff>449178</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>150106</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1668735" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6149,7 +5776,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17366611" y="9261135"/>
+          <a:off x="17512002" y="6873635"/>
           <a:ext cx="1668735" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6200,15 +5827,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>39665</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>55419</xdr:rowOff>
+      <xdr:colOff>66098</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>79442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>50793</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>105656</xdr:rowOff>
+      <xdr:colOff>76599</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>150106</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6227,8 +5854,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18300451" y="8192490"/>
-          <a:ext cx="11128" cy="757809"/>
+          <a:off x="18240236" y="6517028"/>
+          <a:ext cx="10501" cy="254595"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6260,15 +5887,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>163166</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>54763</xdr:rowOff>
+      <xdr:colOff>184298</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>95620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>429941</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>154042</xdr:rowOff>
+      <xdr:colOff>449178</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>145632</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6286,8 +5913,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="17103012" y="9396590"/>
-          <a:ext cx="266775" cy="648798"/>
+          <a:off x="17247122" y="7005914"/>
+          <a:ext cx="264880" cy="236777"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6319,9 +5946,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>109805</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>154042</xdr:rowOff>
+      <xdr:colOff>132218</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>145633</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6337,7 +5964,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16441517" y="10045388"/>
+          <a:off x="16582453" y="7242692"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6388,9 +6015,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>213190</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>126512</xdr:rowOff>
+      <xdr:colOff>235603</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>115488</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6406,7 +6033,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18977440" y="10017858"/>
+          <a:off x="19136191" y="7212547"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6457,15 +6084,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>274271</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>54763</xdr:rowOff>
+      <xdr:colOff>280149</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>95621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>272899</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123337</xdr:rowOff>
+      <xdr:colOff>287684</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>115488</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6483,8 +6110,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19038521" y="9396590"/>
-          <a:ext cx="606763" cy="618093"/>
+          <a:off x="19180737" y="7005915"/>
+          <a:ext cx="620123" cy="206632"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -6516,9 +6143,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>78079</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>134104</xdr:rowOff>
+      <xdr:colOff>100492</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>106344</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6534,7 +6161,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16491158" y="11503946"/>
+          <a:off x="16529674" y="8603799"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6590,9 +6217,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>80126</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>101509</xdr:rowOff>
+      <xdr:colOff>102539</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>73749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6608,7 +6235,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16493205" y="12193246"/>
+          <a:off x="16531721" y="9310113"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6664,15 +6291,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>141367</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>54167</xdr:rowOff>
+      <xdr:colOff>165788</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>40738</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>158386</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>107608</xdr:rowOff>
+      <xdr:colOff>184978</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76672</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6691,8 +6318,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17203541" y="10258341"/>
-          <a:ext cx="17019" cy="417876"/>
+          <a:off x="17206879" y="7429829"/>
+          <a:ext cx="19190" cy="220661"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6724,15 +6351,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>131143</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>37717</xdr:rowOff>
+      <xdr:colOff>153556</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>9956</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>136365</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>104684</xdr:rowOff>
+      <xdr:colOff>158778</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>76924</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6751,8 +6378,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17155827" y="11768506"/>
-          <a:ext cx="5222" cy="427915"/>
+          <a:off x="17194647" y="8876865"/>
+          <a:ext cx="5222" cy="436423"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6783,12 +6410,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>595671</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>58775</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1828139" cy="436786"/>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>5496</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>31014</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1828139" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="115" name="TextBox 114">
@@ -6802,14 +6429,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18769809" y="10726775"/>
-          <a:ext cx="1828139" cy="436786"/>
+          <a:off x="18882314" y="7604832"/>
+          <a:ext cx="1828139" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent1">
+          <a:schemeClr val="accent5">
             <a:lumMod val="20000"/>
             <a:lumOff val="80000"/>
           </a:schemeClr>
@@ -6842,39 +6469,6 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>unallocated</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>_device_ids</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1100" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>.json</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
             <a:rPr lang="en-MY" sz="1100" b="0" u="none">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
@@ -6906,9 +6500,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>231904</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126387</xdr:rowOff>
+      <xdr:colOff>254317</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>92276</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -6924,7 +6518,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18996154" y="11299945"/>
+          <a:off x="19131135" y="8220276"/>
           <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6975,15 +6569,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>265271</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>17542</xdr:rowOff>
+      <xdr:colOff>288363</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>10593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>284565</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>58775</xdr:rowOff>
+      <xdr:colOff>307657</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>31014</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7002,8 +6596,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19778447" y="10476366"/>
-          <a:ext cx="19294" cy="414762"/>
+          <a:off x="19777090" y="7399684"/>
+          <a:ext cx="19294" cy="205148"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7035,15 +6629,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>283985</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>122032</xdr:rowOff>
+      <xdr:colOff>311595</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>117906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>284565</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>126387</xdr:rowOff>
+      <xdr:colOff>317371</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>92276</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7062,8 +6656,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19797161" y="11327914"/>
-          <a:ext cx="580" cy="191120"/>
+          <a:off x="19800322" y="7876451"/>
+          <a:ext cx="5776" cy="343825"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7095,15 +6689,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>32133</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>88022</xdr:rowOff>
+      <xdr:colOff>71544</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>77511</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>53609</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>144644</xdr:rowOff>
+      <xdr:colOff>76599</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>182744</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7122,8 +6716,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18267581" y="7813125"/>
-          <a:ext cx="21476" cy="424485"/>
+          <a:off x="18245682" y="5963304"/>
+          <a:ext cx="5055" cy="289164"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7155,9 +6749,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>37</xdr:col>
-      <xdr:colOff>142288</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>97817</xdr:rowOff>
+      <xdr:colOff>177320</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>27198</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1663960" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -7173,14 +6767,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21339076" y="8157432"/>
+          <a:off x="21395079" y="6280853"/>
           <a:ext cx="1663960" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent1">
+          <a:schemeClr val="accent5">
             <a:lumMod val="20000"/>
             <a:lumOff val="80000"/>
           </a:schemeClr>
@@ -7215,18 +6809,14 @@
           <a:r>
             <a:rPr lang="en-MY" b="1">
               <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>floating_deviceid.json</a:t>
+            <a:t>dbo.DeviceReviewQueue</a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="1" u="none">
             <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -7237,15 +6827,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>369308</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>61234</xdr:rowOff>
+      <xdr:colOff>399949</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>128252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>383021</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>97817</xdr:rowOff>
+      <xdr:colOff>400576</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>27198</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7263,9 +6853,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="22174231" y="7754503"/>
-          <a:ext cx="13713" cy="402929"/>
+        <a:xfrm>
+          <a:off x="22226432" y="6014045"/>
+          <a:ext cx="627" cy="266808"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7297,11 +6887,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>227588</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>12250</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1329337" cy="781240"/>
+      <xdr:colOff>250001</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>169216</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1329337" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="163" name="TextBox 162">
@@ -7315,8 +6905,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19044814" y="11838233"/>
-          <a:ext cx="1329337" cy="781240"/>
+          <a:off x="19126819" y="8851398"/>
+          <a:ext cx="1329337" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7356,7 +6946,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-MY"/>
-            <a:t>Place into Cluster Group Update JSON Print Updated Section</a:t>
+            <a:t>Update SQL MERGE </a:t>
           </a:r>
           <a:endParaRPr lang="en-MY" sz="1100" b="0" u="none"/>
         </a:p>
@@ -7367,15 +6957,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>284122</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>21426</xdr:rowOff>
+      <xdr:colOff>304094</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>170334</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>291613</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>9075</xdr:rowOff>
+      <xdr:colOff>308410</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>169216</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7394,8 +6984,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19656507" y="11561330"/>
-          <a:ext cx="7491" cy="353995"/>
+          <a:off x="19792821" y="8483061"/>
+          <a:ext cx="4316" cy="368337"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7486,87 +7076,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>207749</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>126801</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1762376" cy="248851"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="TextBox 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9547220-EF0A-4C2A-8C17-6429A30A6EF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17232433" y="11857590"/>
-          <a:ext cx="1762376" cy="248851"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>What</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1000" b="1" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> is the cluster algorithm?</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-MY" sz="1000" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>263769</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>104433</xdr:rowOff>
+      <xdr:colOff>286182</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76672</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2206847" cy="609013"/>
     <xdr:sp macro="" textlink="">
@@ -7582,7 +7095,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16100117" y="10673042"/>
+          <a:off x="16103455" y="7650490"/>
           <a:ext cx="2206847" cy="609013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7697,78 +7210,18 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>266665</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>138978</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="900824" cy="248851"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="74" name="TextBox 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D008A83F-C7DB-460A-B447-086CAF236E10}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17264460" y="10322069"/>
-          <a:ext cx="900824" cy="248851"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-MY" sz="1000"/>
-            <a:t>PythonSQL.cs</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>131143</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>175200</xdr:rowOff>
+      <xdr:colOff>153556</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>143704</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>143983</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>134104</xdr:rowOff>
+      <xdr:colOff>166396</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>106344</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7787,8 +7240,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17155827" y="11184095"/>
-          <a:ext cx="12840" cy="319851"/>
+          <a:off x="17194647" y="8271704"/>
+          <a:ext cx="12840" cy="332095"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7820,9 +7273,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>281303</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>151979</xdr:rowOff>
+      <xdr:colOff>303716</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>120484</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2149214" cy="434849"/>
     <xdr:sp macro="" textlink="">
@@ -7838,7 +7291,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16020544" y="13027151"/>
+          <a:off x="16120989" y="9911029"/>
           <a:ext cx="2149214" cy="434849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7968,15 +7421,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>129525</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>8297</xdr:rowOff>
+      <xdr:colOff>151938</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>165264</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>136365</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>151979</xdr:rowOff>
+      <xdr:colOff>158778</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>120484</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7995,8 +7448,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17154209" y="12460981"/>
-          <a:ext cx="6840" cy="324156"/>
+          <a:off x="17193029" y="9586355"/>
+          <a:ext cx="6840" cy="324674"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8025,6 +7478,141 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>346363</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="Rectangle 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67928E0A-A5C6-E8C7-973E-A7072B6F0570}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18645909" y="1801091"/>
+          <a:ext cx="3636818" cy="2297545"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-MY" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>88347</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>176695</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="872435" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="84" name="TextBox 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD481B1A-F27C-4106-9B66-6FE6191CA316}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18221738" y="1634434"/>
+          <a:ext cx="872435" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1" u="none"/>
+            <a:t>Model.dll</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9908,83 +9496,83 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="N2" s="19" t="s">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="N2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="V2" s="19" t="s">
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="V2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
-      <c r="Z2" s="19"/>
-      <c r="AD2" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AD2" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="21"/>
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
     </row>
     <row r="15" spans="2:42" x14ac:dyDescent="0.35">
       <c r="G15" s="1"/>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.35">
       <c r="W43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.35">
       <c r="W44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
     </row>
     <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="20" t="s">
+      <c r="N50" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="20"/>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="20"/>
-      <c r="R50" s="20"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="19"/>
       <c r="V50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="14:26" x14ac:dyDescent="0.35">
       <c r="V51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="14:26" x14ac:dyDescent="0.35">
@@ -9992,7 +9580,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="14:26" x14ac:dyDescent="0.35">
@@ -10015,22 +9603,22 @@
         <v>4</v>
       </c>
       <c r="V56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="14:26" x14ac:dyDescent="0.35">
       <c r="V57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="20" t="s">
+      <c r="N58" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
-      <c r="Q58" s="20"/>
-      <c r="R58" s="20"/>
+      <c r="O58" s="19"/>
+      <c r="P58" s="19"/>
+      <c r="Q58" s="19"/>
+      <c r="R58" s="19"/>
     </row>
     <row r="60" spans="14:26" x14ac:dyDescent="0.35">
       <c r="N60" t="s">
@@ -10052,7 +9640,7 @@
         <v>15</v>
       </c>
       <c r="V63" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="14:26" x14ac:dyDescent="0.35">
@@ -10060,7 +9648,7 @@
         <v>16</v>
       </c>
       <c r="U64" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V64" s="9"/>
       <c r="W64" s="9"/>
@@ -10088,7 +9676,7 @@
         <v>20</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="14:22" x14ac:dyDescent="0.35">
@@ -10096,7 +9684,7 @@
         <v>21</v>
       </c>
       <c r="V69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="14:22" x14ac:dyDescent="0.35">
@@ -10106,18 +9694,18 @@
     </row>
     <row r="84" spans="33:33" x14ac:dyDescent="0.35">
       <c r="AG84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="AD2:AP2"/>
     <mergeCell ref="N58:R58"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="V2:Z2"/>
     <mergeCell ref="N50:R50"/>
-    <mergeCell ref="AD2:AP2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10132,72 +9720,72 @@
   <sheetData>
     <row r="3" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C3" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C4" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C5" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C6" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C7" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C8" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C9" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C10" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="3:3" ht="17.5" x14ac:dyDescent="0.35">
       <c r="C11" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C12" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C13" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C14" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C15" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="3:3" ht="16" x14ac:dyDescent="0.35">
       <c r="C16" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -10218,32 +9806,32 @@
     <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15"/>
       <c r="B1" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>130</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="18" t="s">
         <v>133</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="18" t="s">
         <v>136</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -10265,33 +9853,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" t="s">
         <v>89</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
@@ -10299,19 +9887,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" t="s">
         <v>92</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -10319,19 +9907,19 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" t="s">
         <v>95</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
@@ -10339,19 +9927,19 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>103</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
@@ -10359,30 +9947,30 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" t="s">
         <v>101</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">

--- a/1.training_model/supplementary/1. Flowchart ML development.xlsx
+++ b/1.training_model/supplementary/1. Flowchart ML development.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41250020-B058-42D0-876A-187674F05510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D626908-1957-4AE0-90C0-53A719F552F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Flowchart ML" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="140">
   <si>
     <t>ALPHA_PREFIX_WEIGHT     = 0.65</t>
   </si>
@@ -545,7 +545,10 @@
     <t>dbo.DeviceReviewQueue</t>
   </si>
   <si>
-    <t>Current Workflow Application [28/08/2026]</t>
+    <t>ML pipeline workflow</t>
+  </si>
+  <si>
+    <t>Model Integration [28/08/2026]</t>
   </si>
 </sst>
 </file>
@@ -618,7 +621,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -652,6 +655,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -768,16 +777,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -801,7 +820,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>314655</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>181085</xdr:rowOff>
@@ -882,13 +901,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>149189</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>54230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>157522</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>180260</xdr:rowOff>
@@ -941,7 +960,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>102798</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>178274</xdr:rowOff>
@@ -1036,7 +1055,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>250265</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>177085</xdr:rowOff>
@@ -1125,7 +1144,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>449303</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>122757</xdr:rowOff>
@@ -1220,7 +1239,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>407393</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>24229</xdr:rowOff>
@@ -1301,7 +1320,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>213129</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>979</xdr:rowOff>
@@ -1375,13 +1394,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>149189</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>146635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>166449</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>181449</xdr:rowOff>
@@ -1434,13 +1453,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>162862</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>46824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>166449</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>125932</xdr:rowOff>
@@ -1493,13 +1512,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>162862</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>174479</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>166772</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>27404</xdr:rowOff>
@@ -1552,13 +1571,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>317674</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>66502</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>410568</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>9429</xdr:rowOff>
@@ -1608,7 +1627,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>203326</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>6255</xdr:rowOff>
@@ -1689,7 +1708,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>379604</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>17461</xdr:rowOff>
@@ -1767,13 +1786,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>540161</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>66503</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>87656</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>17461</xdr:rowOff>
@@ -1823,13 +1842,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>317674</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>87628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>333827</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>979</xdr:rowOff>
@@ -1882,7 +1901,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>567293</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>159701</xdr:rowOff>
@@ -1956,13 +1975,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>76523</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>95659</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>87656</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>162876</xdr:rowOff>
@@ -2015,13 +2034,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>333827</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>68848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>76523</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>86245</xdr:rowOff>
@@ -2074,13 +2093,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>150264</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>173264</xdr:rowOff>
@@ -2132,7 +2151,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>37224</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>173264</xdr:rowOff>
@@ -2206,7 +2225,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>501671</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>17114</xdr:rowOff>
@@ -2275,13 +2294,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>450145</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>103080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>450597</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>68505</xdr:rowOff>
@@ -2334,7 +2353,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>23987</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>3143</xdr:rowOff>
@@ -2408,7 +2427,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>199906</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>65330</xdr:rowOff>
@@ -2485,7 +2504,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>396935</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>25727</xdr:rowOff>
@@ -2583,13 +2602,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>450474</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>164664</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>454795</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>3143</xdr:rowOff>
@@ -2642,13 +2661,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>455711</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>89109</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>458327</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>28902</xdr:rowOff>
@@ -2701,7 +2720,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>416072</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>107293</xdr:rowOff>
@@ -2798,13 +2817,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>470171</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>98054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>477464</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>104118</xdr:rowOff>
@@ -2857,7 +2876,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>564013</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>8913</xdr:rowOff>
@@ -2931,13 +2950,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>458327</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>108500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>470171</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>12088</xdr:rowOff>
@@ -2990,7 +3009,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>581476</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>122612</xdr:rowOff>
@@ -3064,13 +3083,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>477464</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>5123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>487634</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>125787</xdr:rowOff>
@@ -3123,16 +3142,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>149225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>133882</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>28937</xdr:rowOff>
+      <xdr:rowOff>25762</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3172,16 +3191,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>511175</xdr:colOff>
       <xdr:row>91</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>105</xdr:row>
-      <xdr:rowOff>30037</xdr:rowOff>
+      <xdr:rowOff>26862</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3221,14 +3240,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>102290</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>105465</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>57699</xdr:rowOff>
     </xdr:to>
@@ -3270,16 +3289,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>251318</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>18804</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>390526</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>387351</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>141782</xdr:rowOff>
+      <xdr:rowOff>144957</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3320,7 +3339,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>145772</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>19739</xdr:rowOff>
@@ -3393,7 +3412,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>487878</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>70523</xdr:rowOff>
@@ -3467,7 +3486,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>142994</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>8612</xdr:rowOff>
@@ -3548,7 +3567,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>128706</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>14168</xdr:rowOff>
@@ -3629,7 +3648,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>477006</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>3327</xdr:rowOff>
@@ -3703,7 +3722,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>571857</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>118817</xdr:rowOff>
@@ -3777,13 +3796,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>401877</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>105705</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>407451</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>67348</xdr:rowOff>
@@ -3836,13 +3855,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>399099</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>153314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>407451</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>11787</xdr:rowOff>
@@ -3895,13 +3914,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>393187</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>92472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>399099</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>121992</xdr:rowOff>
@@ -3954,13 +3973,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>384811</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>29364</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>393187</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>10993</xdr:rowOff>
@@ -4013,13 +4032,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>384811</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>91678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>386339</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>6502</xdr:rowOff>
@@ -4072,7 +4091,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>119976</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>177680</xdr:rowOff>
@@ -4153,7 +4172,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>469007</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>11914</xdr:rowOff>
@@ -4227,13 +4246,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>382431</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>92468</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>386339</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>2261</xdr:rowOff>
@@ -4286,13 +4305,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>375165</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>82947</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>382431</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>8739</xdr:rowOff>
@@ -4345,13 +4364,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>375165</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>94706</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>383332</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>9136</xdr:rowOff>
@@ -4404,7 +4423,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>141188</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>5961</xdr:rowOff>
@@ -4473,7 +4492,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>61092</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>85189</xdr:rowOff>
@@ -4577,7 +4596,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>398389</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>87801</xdr:rowOff>
@@ -4651,7 +4670,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>53731</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>26656</xdr:rowOff>
@@ -4732,7 +4751,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>53551</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>179139</xdr:rowOff>
@@ -4813,13 +4832,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>318867</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>154113</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>319632</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>87801</xdr:rowOff>
@@ -4872,13 +4891,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>311506</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>168430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>319632</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>26656</xdr:rowOff>
@@ -4931,13 +4950,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>311326</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>96667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>311506</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>179139</xdr:rowOff>
@@ -4991,7 +5010,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>55112</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>176493</xdr:rowOff>
@@ -5072,13 +5091,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>311326</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>65218</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>312887</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>176493</xdr:rowOff>
@@ -5132,13 +5151,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>310423</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>66678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>48</xdr:col>
       <xdr:colOff>321281</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>107555</xdr:rowOff>
@@ -5192,7 +5211,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>174334</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>107555</xdr:rowOff>
@@ -5345,7 +5364,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>293601</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>163294</xdr:rowOff>
@@ -5431,7 +5450,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>15599</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>180813</xdr:rowOff>
@@ -5501,7 +5520,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>50</xdr:col>
       <xdr:colOff>344004</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>47623</xdr:rowOff>
@@ -5570,13 +5589,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>71544</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>111187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>174334</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>180812</xdr:rowOff>
@@ -5629,13 +5648,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>50</xdr:col>
       <xdr:colOff>478081</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>111188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>399949</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>47623</xdr:rowOff>
@@ -5688,7 +5707,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>20654</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>182744</xdr:rowOff>
@@ -5757,7 +5776,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>449178</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>150106</xdr:rowOff>
@@ -5826,13 +5845,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>66098</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>79442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>76599</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>150106</xdr:rowOff>
@@ -5886,13 +5905,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>184298</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>95620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>449178</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>145632</xdr:rowOff>
@@ -5945,7 +5964,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>132218</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>145633</xdr:rowOff>
@@ -6014,7 +6033,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>235603</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>115488</xdr:rowOff>
@@ -6083,13 +6102,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>280149</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>95621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>287684</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>115488</xdr:rowOff>
@@ -6142,7 +6161,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>100492</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>106344</xdr:rowOff>
@@ -6216,7 +6235,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>102539</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>73749</xdr:rowOff>
@@ -6290,13 +6309,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>165788</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>40738</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>184978</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>76672</xdr:rowOff>
@@ -6350,13 +6369,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>153556</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>9956</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>158778</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>76924</xdr:rowOff>
@@ -6410,7 +6429,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>5496</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>31014</xdr:rowOff>
@@ -6499,7 +6518,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>254317</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>92276</xdr:rowOff>
@@ -6568,13 +6587,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>288363</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>10593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>307657</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>31014</xdr:rowOff>
@@ -6628,13 +6647,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>311595</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>117906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>317371</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>92276</xdr:rowOff>
@@ -6688,13 +6707,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>71544</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>77511</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>76599</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>182744</xdr:rowOff>
@@ -6748,7 +6767,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>50</xdr:col>
       <xdr:colOff>177320</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>27198</xdr:rowOff>
@@ -6826,13 +6845,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>399949</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>128252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>400576</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>27198</xdr:rowOff>
@@ -6886,7 +6905,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>250001</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>169216</xdr:rowOff>
@@ -6956,13 +6975,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>304094</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>170334</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
+      <xdr:col>47</xdr:col>
       <xdr:colOff>308410</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>169216</xdr:rowOff>
@@ -7016,7 +7035,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>597514</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>160697</xdr:rowOff>
@@ -7076,7 +7095,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>286182</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>76672</xdr:rowOff>
@@ -7212,13 +7231,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>153556</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>143704</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>166396</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>106344</xdr:rowOff>
@@ -7272,7 +7291,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>303716</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>120484</xdr:rowOff>
@@ -7420,13 +7439,13 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>151938</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>165264</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>43</xdr:col>
       <xdr:colOff>158778</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>120484</xdr:rowOff>
@@ -7480,13 +7499,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>138546</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>346363</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>34636</xdr:rowOff>
@@ -7546,7 +7565,7 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>88347</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>176695</xdr:rowOff>
@@ -7613,6 +7632,56 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>565934</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>46475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>245260</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>129874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70776F89-5186-42C3-88EC-C7EF0E527762}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1172070" y="912384"/>
+          <a:ext cx="5134554" cy="7703399"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9486,226 +9555,249 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="B2:AP84"/>
+  <dimension ref="B2:BF84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="2.6328125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="8.7265625" customWidth="1"/>
-    <col min="28" max="28" width="2.6328125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" customWidth="1"/>
+    <col min="13" max="13" width="1.7265625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="2.1796875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="2.6328125" style="2" customWidth="1"/>
+    <col min="40" max="40" width="8.7265625" customWidth="1"/>
+    <col min="41" max="41" width="2.6328125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="4.453125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:42" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:58" x14ac:dyDescent="0.35">
+      <c r="B2" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="26"/>
+      <c r="O2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="N2" s="21" t="s">
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="AA2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="V2" s="21" t="s">
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AI2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AD2" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="21"/>
-      <c r="AM2" s="21"/>
-      <c r="AN2" s="21"/>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AQ2" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR2" s="19"/>
+      <c r="AS2" s="19"/>
+      <c r="AT2" s="19"/>
+      <c r="AU2" s="19"/>
+      <c r="AV2" s="19"/>
+      <c r="AW2" s="19"/>
+      <c r="AX2" s="19"/>
+      <c r="AY2" s="19"/>
+      <c r="AZ2" s="19"/>
+      <c r="BA2" s="19"/>
+      <c r="BB2" s="19"/>
+      <c r="BC2" s="19"/>
+      <c r="BD2" s="24"/>
+      <c r="BE2" s="25"/>
+      <c r="BF2" s="24"/>
     </row>
-    <row r="15" spans="2:42" x14ac:dyDescent="0.35">
-      <c r="G15" s="1"/>
+    <row r="3" spans="2:58" x14ac:dyDescent="0.35">
+      <c r="BC3" s="23"/>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="W43" t="s">
+    <row r="15" spans="2:58" x14ac:dyDescent="0.35">
+      <c r="T15" s="1"/>
+    </row>
+    <row r="43" spans="15:36" x14ac:dyDescent="0.35">
+      <c r="AJ43" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="W44" t="s">
+    <row r="44" spans="15:36" x14ac:dyDescent="0.35">
+      <c r="AJ44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.35">
-      <c r="B48" s="20" t="s">
+    <row r="48" spans="15:36" x14ac:dyDescent="0.35">
+      <c r="O48" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="P48" s="21"/>
+      <c r="Q48" s="21"/>
+      <c r="R48" s="21"/>
     </row>
-    <row r="50" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N50" s="19" t="s">
+    <row r="50" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA50" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O50" s="19"/>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
-      <c r="V50" t="s">
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
+      <c r="AE50" s="20"/>
+      <c r="AI50" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="V51" t="s">
+    <row r="51" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AI51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N52" t="s">
+    <row r="52" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA52" t="s">
         <v>0</v>
       </c>
-      <c r="V52" t="s">
+      <c r="AI52" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N53" t="s">
+    <row r="53" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA53" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N54" t="s">
+    <row r="54" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA54" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N55" t="s">
+    <row r="55" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA55" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N56" t="s">
+    <row r="56" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA56" t="s">
         <v>4</v>
       </c>
-      <c r="V56" t="s">
+      <c r="AI56" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="V57" t="s">
+    <row r="57" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AI57" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N58" s="19" t="s">
+    <row r="58" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA58" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="O58" s="19"/>
-      <c r="P58" s="19"/>
-      <c r="Q58" s="19"/>
-      <c r="R58" s="19"/>
+      <c r="AB58" s="20"/>
+      <c r="AC58" s="20"/>
+      <c r="AD58" s="20"/>
+      <c r="AE58" s="20"/>
     </row>
-    <row r="60" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N60" t="s">
+    <row r="60" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA60" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N61" t="s">
+    <row r="61" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA61" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N62" t="s">
+    <row r="62" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N63" t="s">
+    <row r="63" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA63" t="s">
         <v>15</v>
       </c>
-      <c r="V63" t="s">
+      <c r="AI63" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="14:26" x14ac:dyDescent="0.35">
-      <c r="N64" t="s">
+    <row r="64" spans="27:39" x14ac:dyDescent="0.35">
+      <c r="AA64" t="s">
         <v>16</v>
       </c>
-      <c r="U64" s="8" t="s">
+      <c r="AH64" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="V64" s="9"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
+      <c r="AI64" s="9"/>
+      <c r="AJ64" s="9"/>
+      <c r="AK64" s="9"/>
+      <c r="AL64" s="9"/>
+      <c r="AM64" s="9"/>
     </row>
-    <row r="65" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N65" t="s">
+    <row r="65" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA65" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N66" t="s">
+    <row r="66" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA66" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N67" t="s">
+    <row r="67" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA67" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N68" t="s">
+    <row r="68" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA68" t="s">
         <v>20</v>
       </c>
-      <c r="V68" s="1" t="s">
+      <c r="AI68" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N69" t="s">
+    <row r="69" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA69" t="s">
         <v>21</v>
       </c>
-      <c r="V69" t="s">
+      <c r="AI69" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="14:22" x14ac:dyDescent="0.35">
-      <c r="N70" t="s">
+    <row r="70" spans="27:35" x14ac:dyDescent="0.35">
+      <c r="AA70" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="33:33" x14ac:dyDescent="0.35">
-      <c r="AG84" t="s">
+    <row r="84" spans="46:46" x14ac:dyDescent="0.35">
+      <c r="AT84" t="s">
         <v>137</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="AD2:AP2"/>
-    <mergeCell ref="N58:R58"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="N50:R50"/>
+  <mergeCells count="8">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="AQ2:BC2"/>
+    <mergeCell ref="AA58:AE58"/>
+    <mergeCell ref="O48:R48"/>
+    <mergeCell ref="O2:W2"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="AI2:AM2"/>
+    <mergeCell ref="AA50:AE50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9853,14 +9945,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -9963,14 +10055,14 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
